--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Технический Roadmap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бизнес-функции Roadmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Технический Roadmap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Бизнес-функции Roadmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>verified · command · python3 scripts/ci/roadmap-governance-guard.py; verified · command · python3 scripts/ci/roadmap-governance-guard.py --self-test; verified · artifact · docs/architecture/rm-gov-004-roadmap-governance-guard-design-gate.md</t>
+          <t>verified · command · python3 scripts/ci/roadmap-governance-guard.py; verified · command · python3 scripts/ci/roadmap-governance-guard.py --self-test; verified · ci_run · gh run 33000750265 — roadmap-governance-guard success на 47be5dd; verified · artifact · docs/architecture/rm-gov-004-roadmap-governance-guard-design-gate.md</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); статус verification по решению владельца 2026-08-26: приёмка заявлена verified_by ci_job, а job roadmap-governance-guard ни разу не запускался — ничего не закоммичено. Перевод в done только после commit/push и успешного прогона GitHub Actions; локальные проверки сохранены как evidence.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); приёмочный ci_job подтверждён прогоном GitHub Actions 33000750265 на 47be5dd: job roadmap-governance-guard success, шесть модулей чисты, tamper-матрица 25/25 на раннере; release-gate success. Два предыдущих прогона были красными (32999576636 — lazy-импорт jsonschema и упаковка zip; 33000138974 — сериализация XML через lxml), оба дефекта исправлены, а не обойдены.</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); работа выполнена, статус verification: приёмка заявлена verified_by owner и задача несёт owner_gate canon_change — закрывается утверждением владельца на Gate G. Решения владельца 2026-08-26 по трём развилкам: проза roadmap.md вынесена в четыре документа; legacy-мутаторы перенесены в scripts/legacy с баннером QUARANTINED; job roadmap-consistency-audit удалён, его живые направления перенесены в модуль registry гейта.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); работа выполнена, статус verification: приёмка заявлена verified_by owner и задача несёт owner_gate canon_change — закрывается утверждением владельца на Gate G. Решения владельца 2026-08-26 по трём развилкам: проза roadmap.md вынесена в четыре документа; legacy-мутаторы перенесены в scripts/legacy с баннером QUARANTINED; job roadmap-consistency-audit удалён, его живые направления перенесены в модуль registry гейта. Условие приёмки «CI green» выполнено: прогон 33000750265 на 47be5dd завершён success, 41 job, 0 провалов, release-gate success. Остаётся owner approval на Gate G.</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>verified · command · python3 scripts/ci/roadmap-governance-guard.py; verified · command · python3 scripts/ci/roadmap-governance-guard.py --self-test; verified · artifact · docs/architecture/rm-gov-005-canonical-cutover-design-gate.md</t>
+          <t>verified · command · python3 scripts/ci/roadmap-governance-guard.py; verified · command · python3 scripts/ci/roadmap-governance-guard.py --self-test; verified · ci_run · gh run 33000750265 — release-gate success на 47be5dd; verified · artifact · docs/architecture/rm-gov-005-canonical-cutover-design-gate.md</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); работа выполнена, статус verification: приёмка заявлена verified_by owner и задача несёт owner_gate canon_change — закрывается утверждением владельца на Gate G. Решения владельца 2026-08-26 по трём развилкам: проза roadmap.md вынесена в четыре документа; legacy-мутаторы перенесены в scripts/legacy с баннером QUARANTINED; job roadmap-consistency-audit удалён, его живые направления перенесены в модуль registry гейта. Условие приёмки «CI green» выполнено: прогон 33000750265 на 47be5dd завершён success, 41 job, 0 провалов, release-gate success. Остаётся owner approval на Gate G.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); решения владельца по трём развилкам исполнены; условие CI green выполнено прогоном 33000750265 на 47be5dd (41 job, 0 провалов); Gate G принят владельцем 2026-08-26 после его же проверки, нашедшей ложное срабатывание детектора SUPERSEDED и устаревший текст расхождений — оба исправлены до принятия.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 даёт HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline. Статус verification, не done: owner_gate scope_decision не выдан — решение retire или upgrade по .77 за владельцем, и приёмка прямо оставляет его владельцу.</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
+          <t>verified · ci_run · gh run 33003166965 — roadmap-governance-guard success на 9b88ae8; verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 даёт HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline. Статус verification, не done: owner_gate scope_decision не выдан — решение retire или upgrade по .77 за владельцем, и приёмка прямо оставляет его владельцу.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 дал HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline; DEV/PROD не доказательство по трём проверенным причинам. Owner gate закрыт решением OD-016 от 2026-08-26: владелец вывел .77 из эксплуатации.</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · artifact · tests/behavioral/dsn.py</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS). Tamper-цикл красный в обе стороны. Статус verification, а не done: правка идёт в CI впервые, а я в этой сессии дважды заявлял зелёное, проверив только на своей машине.</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -959,7 +959,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · artifact · tests/behavioral/dsn.py</t>
+          <t>verified · command · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · ci_run · gh run 33006795900 — Behavioral PostgreSQL Tests success на 00d75a6; verified · artifact · tests/behavioral/dsn.py</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS). Tamper-цикл красный в обе стороны. Статус verification, а не done: правка идёт в CI впервые, а я в этой сессии дважды заявлял зелёное, проверив только на своей машине.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS); tamper-цикл красный в обе стороны. Подтверждено на раннере прогоном 33006795900: behavioral 470 passed — ровно столько же, сколько до правки, ни один тест не потерян и не ослаблен.</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона: setup и teardown элевированы, тело теста strict. Замер показал, что на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах; по решению владельца вынесен в отдельную задачу RM-TECH-210, обе записи allowlist названы поимённо и снимаются её починкой.</t>
         </is>
       </c>
     </row>
@@ -2690,31 +2690,31 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; прямой запрос к БД под ролью приложения без контекста находит активный код онбординга [behavioral: `tests/behavioral/test_rls_context_strictness.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2743,14 +2743,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2760,21 +2760,21 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2786,10 +2786,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>не запускается автоматически после pilot [owner]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2806,7 +2810,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2816,21 +2820,21 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Deployment plan/preflight</t>
+          <t>Managed control-plane pilot scope</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2845,7 +2849,7 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2862,58 +2866,114 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Deployment plan/preflight</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner]</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
+          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · ci_run · gh run 33015298420 — Behavioral PostgreSQL Tests success на 1e7a2bf; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона: setup и teardown элевированы, тело теста strict. Замер показал, что на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах; по решению владельца вынесен в отдельную задачу RM-TECH-210, обе записи allowlist названы поимённо и снимаются её починкой.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона. Замер: на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах, по решению владельца вынесен в RM-TECH-210. Подтверждено на раннере прогоном 33015298420: behavioral 475 passed (470 прежних + 5 новых пинов), release-gate success.</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -866,12 +866,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-GOV-007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -881,192 +881,192 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь `.77/.81/DEV/PROD` и очистка активных ссылок</t>
+          <t>Единый реестр решений (A2): DEC как alias owner_decisions, модуль guard decisions</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Gate-G</t>
+          <t>RM-GOV-005</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>versioned environment inventory [artifact: `docs/product/environment-inventory.yaml`]</t>
+          <t>27/27 DEC §29 представлены alias ровно одного OD; guard decisions зелёный [ci_job: `roadmap-governance-guard`]</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>verified · ci_run · gh run 33003166965 — roadmap-governance-guard success на 9b88ae8; verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33164564954</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 дал HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline; DEV/PROD не доказательство по трём проверенным причинам. Owner gate закрыт решением OD-016 от 2026-08-26: владелец вывел .77 из эксплуатации.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-003; SC: SC-GOV-004; DEC: -. Evidence: ci_run 33164564954 (b0f9cdb); docs/audit/2026-08-28-claude-a2-decision-registry.md. Риск регрессии: низкий: только docs/scripts. факт выполнен 2026-08-28 по указанию владельца; done — после owner ACCEPT (EVIDENCE-KIND ci_run есть).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-001</t>
+          <t>RM-GOV-008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Единый контракт `BEHAVIORAL_APP_DB_URL`</t>
+          <t>Трассировка требований (A1): requirements-traceability.yaml + модуль guard req</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-GOV-007</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>обе DSN-формы проходят один targeted behavioral command через один helper [command: `RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q`]</t>
+          <t>101 REQ, 69 SC, 58/58 registry ID трассированы; guard req зелёный [ci_job: `roadmap-governance-guard`]</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>verified · command · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · ci_run · gh run 33006795900 — Behavioral PostgreSQL Tests success на 00d75a6; verified · artifact · tests/behavioral/dsn.py</t>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33166246511</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS); tamper-цикл красный в обе стороны. Подтверждено на раннере прогоном 33006795900: behavioral 470 passed — ровно столько же, сколько до правки, ни один тест не потерян и не ослаблен.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-002, REQ-GOV-003; SC: SC-GOV-003, SC-GOV-004; DEC: -. Evidence: ci_run 33166246511 (d8b6872); docs/audit/2026-08-28-claude-a1-requirements-traceability.md. Риск регрессии: низкий. факт выполнен 2026-08-28; done — после owner ACCEPT.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-GOV-009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Strict RLS context по умолчанию</t>
+          <t>Task breakdown A3 → roadmap.yaml: новые стадии C/CORE/CH/A, перестановка BT, schema stage enum</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-001</t>
+          <t>RM-GOV-008</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>canon_change</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>admin elevation только setup [behavioral: `tests/behavioral/conftest.py::strict get_db default`]</t>
+          <t>все 101 REQ имеют roadmap_ids или approved deferred; traceability без task_required [command: `python3 scripts/ci/roadmap-governance-guard.py`]; владелец принял очередь (ACCEPT с SHA) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · ci_run · gh run 33015298420 — Behavioral PostgreSQL Tests success на 1e7a2bf; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона. Замер: на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах, по решению владельца вынесен в RM-TECH-210. Подтверждено на раннере прогоном 33015298420: behavioral 475 passed (470 прежних + 5 новых пинов), release-gate success.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-003; SC: SC-GOV-004; DEC: -. Evidence: check-roadmap-schema PASS; guard req/decisions PASS; ci_run. Риск регрессии: средний: STAGE_ORDER/schema enum и генерируемые проекции.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003</t>
+          <t>RM-GOV-010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Зафиксировать approved personas/retailer-scope</t>
+          <t>Owner/RACI для REQ и SC (170 TBD) и mapping 23 PENDING-ID journeys</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-GOV-008</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>mini-design/ADR: persona→permissions→scope [owner]</t>
+          <t>0 полей TBD в traceability; pending_journey_map без awaiting_owner [command: `python3 scripts/ci/roadmap-governance-guard.py`]; назначения подтверждены владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1091,42 +1091,42 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-002; SC: SC-GOV-003; DEC: -. Evidence: traceability diff; guard req. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-GOV-011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Реализовать approved RBAC/RLS scope</t>
+          <t>Правила агентов и приёмки: ADR-020 в индекс, Done Gate ↔ §27 DoD требования</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003, RM-STAB-006</t>
+          <t>RM-GOV-006</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>migration_application</t>
+          <t>canon_change</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>API/portal/migration согласованы [behavioral: `tests/behavioral/test_retailer_scope_rbac.py`]</t>
+          <t>индекс Sources of Truth содержит ADR-020; §27 DoD REQ отражён в Done Gate AGENTS.md [artifact: `diff AGENTS.md`]</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1151,38 +1151,38 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-001; SC: SC-GOV-005; DEC: -. Evidence: guard doc PASS; diff AGENTS.md. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-005</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Исправить C1 UI-smoke и расширить общий guard</t>
+          <t>Инвентарь `.77/.81/DEV/PROD` и очистка активных ссылок</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>Gate-G</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1191,58 +1191,62 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>нет API/deep goto/sleep/broad retry [command: `UI_SMOKE_RUN=1 python3 -m pytest tests/ui-contract -q`]</t>
+          <t>versioned environment inventory [artifact: `docs/product/environment-inventory.yaml`]</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · ci_run · gh run 33003166965 — roadmap-governance-guard success на 9b88ae8; verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 дал HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline; DEV/PROD не доказательство по трём проверенным причинам. Owner gate закрыт решением OD-016 от 2026-08-26: владелец вывел .77 из эксплуатации.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-006</t>
+          <t>RM-ENV-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>45/45 нормативных UI journeys</t>
+          <t>Стенд: seed/reset в утверждённое время и точный демо-состав</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1253,7 +1257,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>validator: actor, permission, entry, `Happy-path: N`, selectors, negative expectation [command: `python3 scripts/ci/check-journey-spec.py --strict`]</t>
+          <t>seed/reset воспроизводим, время до smoke-набора измерено и ≤ owner target [command: `tests/test_local_stand.py`]; подсчёт по БД совпадает с §25 REQ-STAND-002 (10/50/500; 2000 KSO …) [behavioral: `tests/test_local_stand.py`]; в seed нет реальных PII/tokens/договоров [command: `tests/test_local_stand.py`]</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1263,42 +1267,42 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-STAND-001, REQ-STAND-002; SC: SC-STAND-001, SC-STAND-002; DEC: -. Evidence: tests/test_local_stand.py; scripts/dev seed report. Риск регрессии: средний: массовый seed может ломать существующие smoke-фикстуры. в A1 STAND-001/002 временно привязаны к RM-STAB-011 — после ACCEPT перепривязать сюда.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-007</t>
+          <t>RM-ENV-003</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>UI proof под intended roles</t>
+          <t>DEV environment manifest (AG): endpoint/версии/SHA/schema/доступность + seed/reset</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-ENV-001, RM-ENV-002</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1309,7 +1313,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>critical journeys имеют positive intended-role и negative missing-permission proof [ui_smoke: `tests/ui-smoke/ci-subset.txt (intended-role variants)`]</t>
+          <t>environment-inventory.yaml содержит поля AG для DEV/.81; guard env зелёный [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1319,14 +1323,14 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-004; SC: SC-OPS-001; DEC: DEC-015. Evidence: guard env; inventory diff. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-008</t>
+          <t>RM-STAB-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1341,16 +1345,16 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Единая blocking-политика UI-smoke</t>
+          <t>Единый контракт `BEHAVIORAL_APP_DB_URL`</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-005, RM-STAB-007</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1359,34 +1363,30 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>canon_change</t>
-        </is>
-      </c>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ordinary pytest отделён [ci_job: `release-gate`]</t>
+          <t>обе DSN-формы проходят один targeted behavioral command через один helper [command: `RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q`]</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · command · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · ci_run · gh run 33006795900 — Behavioral PostgreSQL Tests success на 00d75a6; verified · artifact · tests/behavioral/dsn.py</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS); tamper-цикл красный в обе стороны. Подтверждено на раннере прогоном 33006795900: behavioral 470 passed — ровно столько же, сколько до правки, ни один тест не потерян и не ослаблен.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-009</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Воспроизводимые CI dependencies</t>
+          <t>Strict RLS context по умолчанию</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-STAB-001</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1419,30 +1419,30 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>CI ставит project lock/requirements [ci_job: `python-tests (installs from requirements.txt)`]</t>
+          <t>admin elevation только setup [behavioral: `tests/behavioral/conftest.py::strict get_db default`]</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · ci_run · gh run 33015298420 — Behavioral PostgreSQL Tests success на 1e7a2bf; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона. Замер: на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах, по решению владельца вынесен в RM-TECH-210. Подтверждено на раннере прогоном 33015298420: behavioral 475 passed (470 прежних + 5 новых пинов), release-gate success.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-010</t>
+          <t>RM-STAB-003</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1452,21 +1452,21 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Зафиксировать signing gate</t>
+          <t>Зафиксировать approved personas/retailer-scope</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ADR/roadmap отражают §1.2 [artifact: `docs/architecture/adr/ADR-021-manifest-signing-gate.md`]</t>
+          <t>mini-design/ADR: persona→permissions→scope [owner]</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1491,14 +1495,14 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-011</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1508,21 +1512,21 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>W0 rebaseline</t>
+          <t>Реализовать approved RBAC/RLS scope</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-001, RM-STAB-002, RM-STAB-003, RM-STAB-004, RM-STAB-005, RM-STAB-006, RM-STAB-007, RM-STAB-008, RM-STAB-009, RM-STAB-010</t>
+          <t>RM-STAB-003, RM-STAB-006</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1534,10 +1538,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>named targeted → behavioral → UI subset → guards [command: `python3 scripts/ci/check-roadmap-schema.py --file docs/product/roadmap.yaml`]</t>
+          <t>API/portal/migration согласованы [behavioral: `tests/behavioral/test_retailer_scope_rbac.py`]</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1554,12 +1562,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-STAB-005</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1569,16 +1577,16 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>Исправить C1 UI-smoke и расширить общий guard</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1593,7 +1601,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>нет API/deep goto/sleep/broad retry [command: `UI_SMOKE_RUN=1 python3 -m pytest tests/ui-contract -q`]</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1610,31 +1618,31 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-STAB-006</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Нормативный формат всех UI journeys registry</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-STAB-003</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1649,7 +1657,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>validator: actor, permission, entry, `Happy-path: N`, selectors, negative expectation [command: `python3 scripts/ci/check-journey-spec.py --strict`]; число journeys вычисляется из feature-registry, не фиксируется в задаче (RM-GOV-009 - «45/45» не подтверждено r421) [command: `python3 scripts/roadmap-consistency-check.py`]</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1666,12 +1674,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-STAB-007</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1681,16 +1689,16 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>UI proof под intended roles</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1705,7 +1713,7 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>critical journeys имеют positive intended-role и negative missing-permission proof [ui_smoke: `tests/ui-smoke/ci-subset.txt (intended-role variants)`]</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1722,12 +1730,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-STAB-008</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1737,16 +1745,16 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Единая blocking-политика UI-smoke</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-STAB-005, RM-STAB-007</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1758,10 +1766,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>canon_change</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>ordinary pytest отделён [ci_job: `release-gate`]</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1778,12 +1790,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-STAB-009</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1793,16 +1805,16 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Воспроизводимые CI dependencies</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1829,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>CI ставит project lock/requirements [ci_job: `python-tests (installs from requirements.txt)`]</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1834,31 +1846,31 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-STAB-010</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>Зафиксировать signing gate</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1873,7 +1885,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>ADR/roadmap отражают §1.2 [artifact: `docs/architecture/adr/ADR-021-manifest-signing-gate.md`]</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1883,38 +1895,38 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить alias DEC-003/OD-002, REQ-MAN-002/SEC-003</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-STAB-011</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>W0 rebaseline</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>RM-STAB-001, RM-STAB-002, RM-STAB-003, RM-STAB-004, RM-STAB-005, RM-STAB-006, RM-STAB-007, RM-STAB-008, RM-STAB-009, RM-STAB-010</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1929,7 +1941,7 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human]</t>
+          <t>named targeted → behavioral → UI subset → guards [command: `python3 scripts/ci/check-roadmap-schema.py --file docs/product/roadmap.yaml`]</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1939,42 +1951,42 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): STAND-001/002 перепривязать на RM-ENV-002 после ACCEPT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-STAB-012</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>Async I/O boundary: детектор blocking I/O в async handlers (ADR-012)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Gate-U</t>
+          <t>RM-STAB-009</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1985,7 +1997,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>статический/рантайм-детектор красный на blocking I/O без threadpool; текущий код чист [command: `tests/test_api_tx_boundary.py`]</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1995,19 +2007,19 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-003; SC: SC-ARCH-005; DEC: -. Evidence: tests/test_api_tx_boundary.py; новый lint/pytest. Риск регрессии: средний: может вскрыть существующие blocking-вызовы.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2017,20 +2029,20 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>API attack protection: runtime negative suite (schema/size, IDOR, CSRF/XSS, SSRF, rate limit, headers, no secrets in logs)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2038,14 +2050,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>каждый control имеет negative-тест: красный при отключении, зелёный при включении [behavioral: `tests/test_s065_rate_limit.py`]; 429 + Retry-After по endpoint и principal; audit rate-limit [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2055,19 +2063,19 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-006; SC: SC-SEC-004; DEC: -. Evidence: tests/test_s065_rate_limit.py; tests/test_phase3_security.py; новый negative suite. Риск регрессии: средний: ужесточение headers/CORS может сломать admin-web/advertiser-web.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-STAB-014</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2077,20 +2085,20 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Полнота аудита критичных действий и реальный actor (user/service/device)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2101,7 +2109,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>реестр критичных действий ↔ audit events 100%; anonymous/подставной actor отклонён [behavioral: `tests/behavioral/test_rm_stab_014.py`]</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2111,42 +2119,42 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-005; SC: SC-SEC-003; DEC: -. Evidence: tests/ui-smoke/test_uismoke__audit__view.py; новый behavioral. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-STAB-015</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>Control plane системного администратора: отдельные permission-коды и scope</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Gate-U</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2157,7 +2165,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>users/roles/devices/settings/monitoring/audit — отдельные коды; approved campaign без отдельного права не меняется [behavioral: `tests/test_phase3_user_management.py`]</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2167,19 +2175,19 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-STAB-016</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2189,12 +2197,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Object storage boundary: приватные buckets, presigned TTL, ограниченные service accounts</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2202,7 +2210,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2213,7 +2221,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>анонимный доступ запрещён; просроченный presigned URL отклонён [behavioral: `tests/test_storage_service.py`]</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2223,19 +2231,19 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-007; SC: SC-SEC-005; DEC: -. Evidence: tests/test_storage_service.py; tests/integration/test_minio_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-STAB-017</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2245,12 +2253,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>Независимость production от внешнего runtime: production smoke при выключенных dashboard/LLM-агентах</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-STAB-009</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2258,7 +2266,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2269,7 +2277,7 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>полный production smoke проходит без внешних наблюдателей; ни один сервис не вызывает внешний runtime (egress allow-list) [command: `tests/test_production_config_gate.py`]</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2279,19 +2287,19 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-002; SC: SC-ARCH-004; DEC: DEC-014. Evidence: tests/test_production_config_gate.py; egress check. Риск регрессии: низкий. monitoring-dashboard — read-only наблюдатель (OD-027), не зависимость.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2301,16 +2309,16 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Gate-U</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2322,10 +2330,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; прямой запрос к БД под ролью приложения без контекста находит активный код онбординга [behavioral: `tests/behavioral/test_rls_context_strictness.py`]</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2335,34 +2347,34 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Gate-U</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2370,7 +2382,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2381,7 +2393,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2391,19 +2403,19 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2413,20 +2425,20 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Gate-U</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2437,7 +2449,7 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2447,42 +2459,42 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Gate-U</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2490,14 +2502,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2507,19 +2515,19 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2529,12 +2537,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -2542,7 +2550,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2557,7 +2565,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2567,19 +2575,19 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2589,20 +2597,20 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2612,12 +2620,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2627,34 +2635,34 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -2662,7 +2670,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2673,7 +2681,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2683,19 +2691,19 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2705,12 +2713,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -2718,7 +2726,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2728,12 +2736,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>device_contract</t>
+          <t>migration_application</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; прямой запрос к БД под ролью приложения без контекста находит активный код онбординга [behavioral: `tests/behavioral/test_rls_context_strictness.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2743,42 +2751,42 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2786,14 +2794,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2803,42 +2807,42 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2849,7 +2853,7 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2859,42 +2863,42 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Deployment plan/preflight</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2905,7 +2909,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2915,65 +2919,3713 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>RM-TECH-230</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-220</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-001</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Записать managed-first scope</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-201</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Таксономия причин недопоказа</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-202</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Вытеснение и объяснимые приоритеты</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-201</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-203</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Overbooking policy</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-202</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-204</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Creative QA без неутверждённого HTML5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-206</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>License renewal/grant boundary</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-240</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-229</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-241</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-240</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-242</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-240</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-243</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-242</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-244</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-243</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-245</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-004</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-246</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-004</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-247</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-245</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-248</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-245</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-249</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-248</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-250</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-204</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-251</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-229</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-252</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-004</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-253</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-229</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-254</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-245</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-255</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-224</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-002</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>`self.campaign_create` в будущей ветке</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-001</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-001</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-002</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-001</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-003</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Responsive-проверка (A4)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-002</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-004</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Согласованность состояний и терминов (A6)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-003</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-005</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-004</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-006</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-005</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-007</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Human operator walkthrough (A7)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>человек проходит exact stand bundle [human]</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-008</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-249, RM-UX-004</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-009</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-250</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-011</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-004, RM-STAB-006</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207A</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>KSO environment + player/playlist design</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207B</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>KSO player/playlist/PoP chain</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207A</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-208</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Signed licensing Layer 2</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-260</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207B</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-261</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207B, RM-TECH-230</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-262</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-280, RM-TECH-261</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. blocked: ложная ESL-посылка, master adapter (OD-023).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-263</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-210, RM-TECH-255</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. blocked RM-TECH-210.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-264</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-280</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. blocked OD-023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-280</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-229</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; blocked до имени владельца.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-003</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>`self.report_view` plan/fact</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-201, RM-TECH-207B</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-205</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>SLO objectives и измерение</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-209</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>ClickHouse capacity trigger</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207B</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-256</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-205</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-281</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-280</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. blocked RM-TECH-280.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-282</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-281, RM-TECH-229</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-283</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-280, RM-TECH-253</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-284</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-282</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-285</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-202, RM-TECH-280</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-286</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-246</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-287</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>RM-STAB-013</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-288</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-205</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-289</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-220</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-010</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-003</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-001</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Production readiness</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="F101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>не запускается автоматически после pilot [owner]</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-002</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-003</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-001</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-004</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-005</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-253</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Managed control-plane pilot scope</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Deployment plan/preflight</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-003</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner]</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
@@ -2990,7 +6642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3628,7 +7280,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>audit.view</t>
+          <t>analytics.compare</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3638,7 +7290,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Смотреть журнал аудита</t>
+          <t>Отчёт качества услуги по каналам (plan/fact, доля active devices)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3653,22 +7305,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__audit__view</t>
+          <t>test_uismoke__analytics__compare</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3676,14 +7328,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-UX-010 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>RM-UX-010</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-UX-010 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>campaign.activate</t>
+          <t>attribution.lift_report</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -3693,12 +7357,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Запустить одобренную кампанию</t>
+          <t>Отчёт sales lift test/control (attribution)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3708,22 +7372,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__activate</t>
+          <t>test_uismoke__attribution__lift_report</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3731,14 +7395,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-282 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-282</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-282 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>campaign.approve</t>
+          <t>audit.view</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3748,12 +7424,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Одобрить кампанию</t>
+          <t>Смотреть журнал аудита</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3763,7 +7439,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__approve</t>
+          <t>test_uismoke__audit__view</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3793,7 +7469,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>campaign.create</t>
+          <t>campaign.activate</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3803,12 +7479,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Создание кампании</t>
+          <t>Запустить одобренную кампанию</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -3818,7 +7494,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__create</t>
+          <t>test_uismoke__campaign__activate</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3848,7 +7524,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>campaign.edit</t>
+          <t>campaign.approve</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3858,7 +7534,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Редактирование кампании (рейсы/размещения)</t>
+          <t>Одобрить кампанию</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3873,7 +7549,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__edit</t>
+          <t>test_uismoke__campaign__approve</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3903,7 +7579,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>campaign.pause</t>
+          <t>campaign.create</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -3913,12 +7589,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Приостановить активную кампанию</t>
+          <t>Создание кампании</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -3928,7 +7604,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__pause</t>
+          <t>test_uismoke__campaign__create</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3958,7 +7634,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>campaign.reject</t>
+          <t>campaign.edit</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3968,7 +7644,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Отклонить кампанию с причиной</t>
+          <t>Редактирование кампании (рейсы/размещения)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3983,7 +7659,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__reject</t>
+          <t>test_uismoke__campaign__edit</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4013,7 +7689,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>campaign.submit</t>
+          <t>campaign.pause</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -4023,12 +7699,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Отправить кампанию на согласование</t>
+          <t>Приостановить активную кампанию</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4038,7 +7714,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__campaign__submit</t>
+          <t>test_uismoke__campaign__pause</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4068,7 +7744,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>commerce.booking</t>
+          <t>campaign.readiness</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -4078,7 +7754,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Бронирование (offered→booked)</t>
+          <t>Матрица готовности кампании по каналам</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4088,27 +7764,27 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__campaign__readiness</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4116,14 +7792,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-249 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-249</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-249 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>commerce.offer_generate</t>
+          <t>campaign.reject</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -4133,22 +7821,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Генерация коммерческого предложения (draft→offered)</t>
+          <t>Отклонить кампанию с причиной</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__campaign__reject</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4178,7 +7866,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>commerce.order_close</t>
+          <t>campaign.schedule</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -4188,7 +7876,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Закрытие заказа (terminal)</t>
+          <t>Flight/placement windows кампании (versioned, UTC + local TZ)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4198,27 +7886,27 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__campaign__schedule</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4226,14 +7914,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-248 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-248</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-248 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>commerce.order_create</t>
+          <t>campaign.submit</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -4243,22 +7943,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Создание коммерческого заказа</t>
+          <t>Отправить кампанию на согласование</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__campaign__submit</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4288,7 +7988,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>commerce.payment_status</t>
+          <t>commerce.booking</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -4298,7 +7998,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Статус оплаты заказа</t>
+          <t>Бронирование (offered→booked)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4343,7 +8043,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>commerce.price_list_manage</t>
+          <t>commerce.offer_generate</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -4353,7 +8053,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Управление версиями прайс-листов</t>
+          <t>Генерация коммерческого предложения (draft→offered)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -4363,12 +8063,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__tariff_manage</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4398,7 +8098,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>commerce.tariff_manage</t>
+          <t>commerce.order_close</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4408,7 +8108,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Управление тарифами и прайс-листами</t>
+          <t>Закрытие заказа (terminal)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4418,12 +8118,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__tariff_manage</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4453,7 +8153,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>creative.moderate_approve</t>
+          <t>commerce.order_create</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -4463,22 +8163,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Одобрить креатив (модерация)</t>
+          <t>Создание коммерческого заказа</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__creative__moderate_approve</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4508,7 +8208,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>creative.moderate_reject</t>
+          <t>commerce.payment_status</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -4518,22 +8218,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Отклонить креатив с причиной (модерация)</t>
+          <t>Статус оплаты заказа</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__creative__moderate_reject</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4563,7 +8263,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>creative.upload</t>
+          <t>commerce.price_list_manage</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -4573,22 +8273,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Загрузка креатива</t>
+          <t>Управление версиями прайс-листов</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__creative__upload</t>
+          <t>test_uismoke__commerce__tariff_manage</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4618,7 +8318,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>device.health_view</t>
+          <t>commerce.tariff_manage</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4628,7 +8328,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Видеть состояние парка устройств</t>
+          <t>Управление тарифами и прайс-листами</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4638,12 +8338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/commerce/tariffs</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__device__health_view</t>
+          <t>test_uismoke__commerce__tariff_manage</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4673,7 +8373,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>emergency.activate</t>
+          <t>creative.moderate_approve</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -4683,7 +8383,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Экстренно остановить показ</t>
+          <t>Одобрить креатив (модерация)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4698,7 +8398,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__emergency__activate</t>
+          <t>test_uismoke__creative__moderate_approve</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4721,18 +8421,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Platform/backend emergency state + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>emergency.deactivate</t>
+          <t>creative.moderate_reject</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4742,7 +8438,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Снять аварийный режим</t>
+          <t>Отклонить креатив с причиной (модерация)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4757,7 +8453,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__emergency__deactivate</t>
+          <t>test_uismoke__creative__moderate_reject</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4780,18 +8476,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Platform/backend deactivation + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
-        </is>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>inventory.rule_create</t>
+          <t>creative.upload</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4801,12 +8493,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Создать правило инвентаря</t>
+          <t>Загрузка креатива</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4816,7 +8508,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__inventory__rule_create</t>
+          <t>test_uismoke__creative__upload</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4846,7 +8538,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>inventory.simulate</t>
+          <t>device.health_view</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4856,7 +8548,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Прогноз показов (симуляция инвентаря)</t>
+          <t>Видеть состояние парка устройств</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4871,7 +8563,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__inventory__simulate</t>
+          <t>test_uismoke__device__health_view</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4901,7 +8593,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>system.theme_switch</t>
+          <t>emergency.activate</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -4911,22 +8603,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Переключение темы (light/dark)</t>
+          <t>Экстренно остановить показ</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sidebar footer toggle</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__system__theme_switch</t>
+          <t>test_uismoke__emergency__activate</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4949,14 +8641,18 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Platform/backend emergency state + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>user.assign_roles</t>
+          <t>emergency.deactivate</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4966,7 +8662,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Назначить роли/права пользователю</t>
+          <t>Снять аварийный режим</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4981,7 +8677,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__assign_roles</t>
+          <t>test_uismoke__emergency__deactivate</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5004,14 +8700,18 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Platform/backend deactivation + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>user.create_advertiser</t>
+          <t>experiment.evaluate</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -5021,12 +8721,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Завести локального рекламодателя</t>
+          <t>A/B: группы, период, winner metric, ручное утверждение результата</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5036,22 +8736,22 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__create_advertiser</t>
+          <t>test_uismoke__experiment__evaluate</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -5059,14 +8759,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-284 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-284</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-284 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>user.deactivate</t>
+          <t>field_ops.device_confirm</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5076,12 +8788,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Заблокировать пользователя</t>
+          <t>Полевые операции: устройства магазина, фото, инциденты (mobile web)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5091,22 +8803,22 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__deactivate</t>
+          <t>test_uismoke__field_ops__device_confirm</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5114,14 +8826,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-263 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-263</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-263 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>user.reset_password</t>
+          <t>finance.reconcile</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -5131,12 +8855,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Сбросить пароль пользователю</t>
+          <t>Финансовая сверка: заказ/договор/тариф/price list</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5146,22 +8870,22 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__reset_password</t>
+          <t>test_uismoke__finance__reconcile</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -5169,14 +8893,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-286 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-286</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-286 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>user.split_internal_advertiser</t>
+          <t>inventory.rule_create</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -5186,7 +8922,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Разделить пользователей на внутренних и рекламодателей</t>
+          <t>Создать правило инвентаря</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5201,7 +8937,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__split_internal_advertiser</t>
+          <t>test_uismoke__inventory__rule_create</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5231,17 +8967,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>self.apply_or_brief</t>
+          <t>inventory.simulate</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Подать заявку/бриф (кабинет рекламодателя)</t>
+          <t>Прогноз показов (симуляция инвентаря)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5256,7 +8992,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__apply_or_brief</t>
+          <t>test_uismoke__inventory__simulate</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5286,17 +9022,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>self.campaign_create</t>
+          <t>kpi.review</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Самому завести кампанию (self-service, P2)</t>
+          <t>Бизнес-KPI: baseline/target/metric по целям §1.2</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5311,7 +9047,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__campaign_create</t>
+          <t>test_uismoke__kpi__review</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5336,39 +9072,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>UI-smoke отсутствует. P2 — self-service фаза, не пилот.</t>
+          <t>Запланировано задачей RM-TECH-256 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>владелец включает self-service в scope пилота</t>
+          <t>функция реализована задачей RM-TECH-256 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>self.campaign_view</t>
+          <t>placement.audience_targeting</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Смотреть свои кампании (кабинет рекламодателя)</t>
+          <t>Store-audience targeting по анонимным атрибутам магазина</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5378,22 +9114,22 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__campaign_view</t>
+          <t>test_uismoke__placement__audience_targeting</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5401,54 +9137,66 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-283 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-283</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-283 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>self.login</t>
+          <t>rollout.rollback</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Войти в кабинет рекламодателя</t>
+          <t>Staged rollout и rollback с feature flags</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>/login (advertiser-web) + /accept-invite/{token}</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__login</t>
+          <t>test_uismoke__rollout__rollback</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5456,54 +9204,66 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-OPS-004 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-004</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-OPS-004 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>self.report_view</t>
+          <t>system.theme_switch</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Смотреть отчёт план/факт (PoP) — кабинет рекламодателя</t>
+          <t>Переключение темы (light/dark)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>sidebar footer toggle</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__report_view</t>
+          <t>test_uismoke__system__theme_switch</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5511,51 +9271,39 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>UI-smoke отсутствует. Фронтенд advertiser-web не проходил аудит.</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>RM-BIZ-003</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>реальные PoP-события от плеера, а не симулятора</t>
-        </is>
-      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>advertiser.apply</t>
+          <t>user.assign_roles</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Подать заявку на подключение (публичная форма)</t>
+          <t>Назначить роли/права пользователю</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>/become-advertiser</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__advertiser__apply</t>
+          <t>test_uismoke__user__assign_roles</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5585,42 +9333,42 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>backup.restore</t>
+          <t>user.create_advertiser</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Резервное копирование и восстановление</t>
+          <t>Завести локального рекламодателя</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>001C-FU: test_restore_drill_verify.py (16 behavioral) + test_backup_restore_drill.py (27 negative matrix) — real PG+MinIO drill</t>
+          <t>test_uismoke__user__create_advertiser</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5633,28 +9381,24 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Pilot host restore drill всё ещё требуется перед реальным деплоем (001D/001E). NATS = excluded_replayable (outbox source of truth).</t>
-        </is>
-      </c>
+      <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>campaign.complete</t>
+          <t>user.deactivate</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Автоматическое завершение кампании по концу рейса</t>
+          <t>Заблокировать пользователя</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5664,22 +9408,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>POST /campaigns/{id}/complete, POST /campaigns/complete-expired</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>n/a (service feature, no UI journey)</t>
+          <t>test_uismoke__user__deactivate</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -5692,53 +9436,49 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>LIFECYCLE-COMPLETE-001-FU: real DB proof. 7 behavioral tests green. Orchestrator-worker maintenance tick (5 min). CampaignStatusHistory verified. Idempotency proven.</t>
-        </is>
-      </c>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>device.heartbeat</t>
+          <t>user.reset_password</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat устройств (health/статус)</t>
+          <t>Сбросить пароль пользователю</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>EDGE-004 behavioral (12 тестов): test_edge004_*.py</t>
+          <t>test_uismoke__user__reset_password</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -5758,42 +9498,42 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>device.onboard</t>
+          <t>user.split_internal_advertiser</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Онбординг устройства (device-code → JWT)</t>
+          <t>Разделить пользователей на внутренних и рекламодателей</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>EDGE-001 behavioral (13 тестов): test_edge001_*.py</t>
+          <t>test_uismoke__user__split_internal_advertiser</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5813,17 +9553,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>license.enforce</t>
+          <t>self.apply_or_brief</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Enforcement лицензии при device enrollment</t>
+          <t>Подать заявку/бриф (кабинет рекламодателя)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -5833,22 +9573,22 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard (enrollment choke-point)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>test_license_enrollment.py (13 behavioral tests)</t>
+          <t>test_uismoke__self__apply_or_brief</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -5868,32 +9608,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>license.report</t>
+          <t>self.campaign_create</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Отчёт по лицензии (занятые/свободные seats + пик)</t>
+          <t>Самому завести кампанию (self-service, P2)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>GET /licenses/report?year&amp;month</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>test_license_report.py (16 behavioral tests)</t>
+          <t>test_uismoke__self__campaign_create</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5908,7 +9648,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -5916,49 +9656,61 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>UI-smoke отсутствует. P2 — self-service фаза, не пилот.</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-002</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>владелец включает self-service в scope пилота</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>license.seat_release</t>
+          <t>self.campaign_view</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Освобождение лицензионного seat при decommission</t>
+          <t>Смотреть свои кампании (кабинет рекламодателя)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>POST /devices/{device_id}/decommission</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>test_license_decommission.py (13 behavioral tests)</t>
+          <t>test_uismoke__self__campaign_view</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -5978,47 +9730,47 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>license.upload</t>
+          <t>self.login</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Загрузка/установка лицензионного файла</t>
+          <t>Войти в кабинет рекламодателя</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login (advertiser-web) + /accept-invite/{token}</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>test_uismoke__self__login</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6026,36 +9778,24 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Layer 2 (signed-license/JWS/CRL + UI upload) — не реализован.</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-208</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>signed-license Layer 2: upload .lic + проверка подписи</t>
-        </is>
-      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>license.view</t>
+          <t>self.report_view</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Просмотр активных лицензий (UI)</t>
+          <t>Смотреть отчёт план/факт (PoP) — кабинет рекламодателя</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6065,12 +9805,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>test_uismoke__self__report_view</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6095,59 +9835,59 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Layer 2 (signed-license/UI) — не реализован.</t>
+          <t>UI-smoke отсутствует. Фронтенд advertiser-web не проходил аудит.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>signed-license Layer 2: offline Ed25519 verify + kid/CRL</t>
+          <t>реальные PoP-события от плеера, а не симулятора</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>manifest.deliver</t>
+          <t>advertiser.apply</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Доставка манифеста на устройство</t>
+          <t>Подать заявку на подключение (публичная форма)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/become-advertiser</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>EDGE-002 behavioral (13 тестов): test_edge002_*.py</t>
+          <t>test_uismoke__advertiser__apply</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6167,7 +9907,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>observability</t>
+          <t>backup.restore</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6177,7 +9917,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Мониторинг и метрики (Prometheus/Grafana)</t>
+          <t>Резервное копирование и восстановление</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -6192,7 +9932,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>S-047: /metrics endpoint, Prometheus alert rules (8 rules)</t>
+          <t>001C-FU: test_restore_drill_verify.py (16 behavioral) + test_backup_restore_drill.py (27 negative matrix) — real PG+MinIO drill</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6217,7 +9957,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>AlertManager routing deferred, но метрики и алерты существуют.</t>
+          <t>Pilot host restore drill всё ещё требуется перед реальным деплоем (001D/001E). NATS = excluded_replayable (outbox source of truth).</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
@@ -6226,7 +9966,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>playlist.build</t>
+          <t>campaign.competitive_separation</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6236,12 +9976,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Построение плейлиста из манифеста</t>
+          <t>Competitive separation при построении playlist/manifest</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6251,7 +9991,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>behavioral: tests/behavioral/test_rm_tech_285.py</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6276,24 +10016,24 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Плеер не перенесён в enterprise. Код есть в старом репо (PLAYER-AUD-001), адаптация — после manifest/onboard/ingest.</t>
+          <t>Запланировано задачей RM-TECH-285 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>плеер перенесён в enterprise-репозиторий и есть реальный КСО</t>
+          <t>функция реализована задачей RM-TECH-285 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>pop.ingest</t>
+          <t>campaign.complete</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6303,22 +10043,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Приём PoP-событий от устройств</t>
+          <t>Автоматическое завершение кампании по концу рейса</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /campaigns/{id}/complete, POST /campaigns/complete-expired</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>EDGE-003 behavioral (11 тестов): test_edge003_*.py</t>
+          <t>n/a (service feature, no UI journey)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6341,9 +10081,938 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>LIFECYCLE-COMPLETE-001-FU: real DB proof. 7 behavioral tests green. Orchestrator-worker maintenance tick (5 min). CampaignStatusHistory verified. Idempotency proven.</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>content.dynamic_binding</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic creative: подстановка master-confirmed price/promo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>behavioral: tests/behavioral/test_rm_tech_262.py</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-262 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-262</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-262 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>device.heartbeat</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Heartbeat устройств (health/статус)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>EDGE-004 behavioral (12 тестов): test_edge004_*.py</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>device.onboard</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Онбординг устройства (device-code → JWT)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>EDGE-001 behavioral (13 тестов): test_edge001_*.py</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>OD-038 / RLS-CONTEXT-DEVICE-001: в production-path устройство получает 403 INVALID_CODE — маршрут без RLS-контекста; reachable держался под admin-маской тестов. Unblock: RM-TECH-210 (behavioral под runtime-ролью на PostgreSQL).</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-210</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>POST /device/onboard и POST /identity/device-codes работают под runtime-ролью на PostgreSQL без элевации (behavioral evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>finance.exchange</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Обмен с финансовой системой: idempotent export + payment-status</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>behavioral: tests/behavioral/test_rm_tech_286.py</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-286 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-286</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-286 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>integration.reconcile</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Ingestion агрегатов чековых данных и сверка с master-данными</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>behavioral: tests/behavioral/test_rm_tech_281.py</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-281 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-281</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-281 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>license.enforce</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Enforcement лицензии при device enrollment</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>POST /device/onboard (enrollment choke-point)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>test_license_enrollment.py (13 behavioral tests)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>license.report</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Отчёт по лицензии (занятые/свободные seats + пик)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>GET /licenses/report?year&amp;month</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>test_license_report.py (16 behavioral tests)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>license.seat_release</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение лицензионного seat при decommission</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>POST /devices/{device_id}/decommission</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>test_license_decommission.py (13 behavioral tests)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>license.upload</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Загрузка/установка лицензионного файла</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Layer 2 (signed-license/JWS/CRL + UI upload) — не реализован.</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-208</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>signed-license Layer 2: upload .lic + проверка подписи</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>license.view</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Просмотр активных лицензий (UI)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Layer 2 (signed-license/UI) — не реализован.</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-208</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>signed-license Layer 2: offline Ed25519 verify + kid/CRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>manifest.deliver</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Доставка манифеста на устройство</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>EDGE-002 behavioral (13 тестов): test_edge002_*.py</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>observability</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Мониторинг и метрики (Prometheus/Grafana)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>S-047: /metrics endpoint, Prometheus alert rules (8 rules)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>AlertManager routing deferred, но метрики и алерты существуют.</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>playlist.build</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Построение плейлиста из манифеста</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Плеер не перенесён в enterprise. Код есть в старом репо (PLAYER-AUD-001), адаптация — после manifest/onboard/ingest.</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207B</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>плеер перенесён в enterprise-репозиторий и есть реальный КСО</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>pop.ingest</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Приём PoP-событий от устройств</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>EDGE-003 behavioral (11 тестов): test_edge003_*.py</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>release.rollback</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Rollback релиза по плану развёртывания</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>behavioral: tests/behavioral/test_rm_ops_004.py</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-OPS-004 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-004</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-OPS-004 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33169752021</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-002; SC: SC-GOV-003; DEC: -. Evidence: traceability diff; guard req. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-GOV-002; SC: SC-GOV-003; DEC: -. Evidence: traceability diff; guard req. Риск регрессии: низкий. 2026-08-31: owner mapping применён по OD-039 (170 TBD → 0, OD-023 approved); остаток - mapping PENDING-ID journeys (8 awaiting_owner). OD-040 (2026-08-31): pending_journey_map закрыт - 6 новых blocked registry-ID, audit.compare rejected, security.review → audit.view; приёмка (1)/(2) выполнена локально, verification - после CI-прогона.</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-GOV-012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1173,16 +1173,16 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь `.77/.81/DEV/PROD` и очистка активных ссылок</t>
+          <t>Выравнивание ТЗ v2.6 ↔ roadmap ↔ хронология ↔ зависимости ↔ acceptance gates; единый план реализации (без кода)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Gate-G</t>
+          <t>RM-GOV-010</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1191,34 +1191,34 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>canon_change</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>versioned environment inventory [artifact: `docs/product/environment-inventory.yaml`]</t>
+          <t>единый план реализации опубликован и привязан к SHA roadmap.yaml/ТЗ; расхождения ТЗ↔roadmap↔gates закрыты или названы с владельцем [artifact: `docs/product/implementation-plan-v2.6.md`]; независимая проверка Codex выполнена, замечания закрыты [artifact: `docs/audit/&lt;дата&gt;-codex-review-implementation-plan.md`]; документы утверждены владельцем (ACCEPT с датой) - стадия C и Gate-C становятся точкой старта разработки [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; schema/consistency/governance/self-test зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>verified · ci_run · gh run 33003166965 — roadmap-governance-guard success на 9b88ae8; verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 дал HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline; DEV/PROD не доказательство по трём проверенным причинам. Owner gate закрыт решением OD-016 от 2026-08-26: владелец вывел .77 из эксплуатации.</t>
+          <t>По указанию владельца 2026-08-31 (OD-041). Предложения этой задачи, требующие ACCEPT: гейты Gate-CORE/CH/A/POPS, расширение условий Gate-C, перенос RM-TECH-205/288/253, RM-OPS-005, RM-UX-011 в стадию C, новая RM-TECH-231. Механические выравнивания (feature_ids, refs приёмки, RM-TECH-263 planned, RM-TECH-284 OD-014, REQ blocked ⇔ задачи blocked) применены. REQ: REQ-GOV-001, REQ-GOV-003; SC: SC-GOV-001; DEC: -. Evidence: план; guard. Риск регрессии: нет (документы/SSOT). OD-042 (2026-08-31): процесс и предложения утверждены владельцем; добавлены implementation_mode/code_baseline/regression_criteria у 101 REQ.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-002</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1228,21 +1228,21 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Стенд: seed/reset в утверждённое время и точный демо-состав</t>
+          <t>Инвентарь `.77/.81/DEV/PROD` и очистка активных ссылок</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>Gate-G</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1251,30 +1251,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>seed/reset воспроизводим, время до smoke-набора измерено и ≤ owner target [command: `tests/test_local_stand.py`]; подсчёт по БД совпадает с §25 REQ-STAND-002 (10/50/500; 2000 KSO …) [behavioral: `tests/test_local_stand.py`]; в seed нет реальных PII/tokens/договоров [command: `tests/test_local_stand.py`]</t>
+          <t>versioned environment inventory [artifact: `docs/product/environment-inventory.yaml`]</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · ci_run · gh run 33003166965 — roadmap-governance-guard success на 9b88ae8; verified · artifact · docs/product/environment-inventory.yaml; verified · command · curl -s -o /dev/null -w '%{http_code}' --max-time 4 http://192.168.110.77:3000/; verified · command · curl -s http://192.168.110.81:8000/version; verified · command · python3 scripts/ci/roadmap-governance-guard.py --module env; verified · artifact · docs/architecture/rm-env-001-environment-inventory-design-gate.md</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-STAND-001, REQ-STAND-002; SC: SC-STAND-001, SC-STAND-002; DEC: -. Evidence: tests/test_local_stand.py; scripts/dev seed report. Риск регрессии: средний: массовый seed может ломать существующие smoke-фикстуры. в A1 STAND-001/002 временно привязаны к RM-STAB-011 — после ACCEPT перепривязать сюда.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); инвентарь собран из собственных прогонов: .77 дал HTTP 000 на трёх портах, .81 отдаёт stand-27dc397/schema 036 и совпадает с base.stand_baseline; DEV/PROD не доказательство по трём проверенным причинам. Owner gate закрыт решением OD-016 от 2026-08-26: владелец вывел .77 из эксплуатации.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-003</t>
+          <t>RM-ENV-002</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1284,21 +1288,21 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DEV environment manifest (AG): endpoint/версии/SHA/schema/доступность + seed/reset</t>
+          <t>Стенд: seed/reset в утверждённое время и точный демо-состав</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001, RM-ENV-002</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1313,7 +1317,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>environment-inventory.yaml содержит поля AG для DEV/.81; guard env зелёный [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>seed/reset воспроизводим, время до smoke-набора измерено и ≤ owner target [command: `tests/test_local_stand.py`]; подсчёт по БД совпадает с §25 REQ-STAND-002 (10/50/500; 2000 KSO …) [behavioral: `tests/test_local_stand.py`]; в seed нет реальных PII/tokens/договоров [command: `tests/test_local_stand.py`]</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1323,38 +1327,38 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-004; SC: SC-OPS-001; DEC: DEC-015. Evidence: guard env; inventory diff. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-STAND-001, REQ-STAND-002; SC: SC-STAND-001, SC-STAND-002; DEC: -. Evidence: tests/test_local_stand.py; scripts/dev seed report. Риск регрессии: средний: массовый seed может ломать существующие smoke-фикстуры. в A1 STAND-001/002 временно привязаны к RM-STAB-011 — после ACCEPT перепривязать сюда.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-001</t>
+          <t>RM-ENV-003</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Единый контракт `BEHAVIORAL_APP_DB_URL`</t>
+          <t>DEV environment manifest (AG): endpoint/версии/SHA/schema/доступность + seed/reset</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-ENV-001, RM-ENV-002</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1363,30 +1367,34 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>обе DSN-формы проходят один targeted behavioral command через один helper [command: `RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q`]</t>
+          <t>environment-inventory.yaml содержит поля AG для DEV/.81; guard env зелёный [command: `python3 scripts/ci/roadmap-governance-guard.py`]; DEV environment manifest принят владельцем как артефакт Дополнения AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>verified · command · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · ci_run · gh run 33006795900 — Behavioral PostgreSQL Tests success на 00d75a6; verified · artifact · tests/behavioral/dsn.py</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS); tamper-цикл красный в обе стороны. Подтверждено на раннере прогоном 33006795900: behavioral 470 passed — ровно столько же, сколько до правки, ни один тест не потерян и не ослаблен.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-004; SC: SC-OPS-001; DEC: DEC-015. Evidence: guard env; inventory diff. Риск регрессии: низкий. Закрывает Gate-E0 (RM-GOV-012, 2026-08-31).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1401,16 +1409,16 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Strict RLS context по умолчанию</t>
+          <t>Единый контракт `BEHAVIORAL_APP_DB_URL`</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-001</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1425,24 +1433,24 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>admin elevation только setup [behavioral: `tests/behavioral/conftest.py::strict get_db default`]</t>
+          <t>обе DSN-формы проходят один targeted behavioral command через один helper [command: `RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q`]</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · ci_run · gh run 33015298420 — Behavioral PostgreSQL Tests success на 1e7a2bf; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
+          <t>verified · command · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral/test_commerce_rls.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 BEHAVIORAL_APP_DB_URL=postgresql+asyncpg://... python3 -m pytest tests/behavioral/test_commerce_rls.py tests/behavioral/test_campaign_permission_split_001.py -q; verified · behavioral · tamper — helper перестаёт нормализовать в каждую сторону; verified · ci_run · gh run 33006795900 — Behavioral PostgreSQL Tests success на 00d75a6; verified · artifact · tests/behavioral/dsn.py</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона. Замер: на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах, по решению владельца вынесен в RM-TECH-210. Подтверждено на раннере прогоном 33015298420: behavioral 475 passed (470 прежних + 5 новых пинов), release-gate success.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ENV-CONTRACT-001. Один helper tests/behavioral/dsn.py, 12 потребителей переведены. Обе DSN-формы прошли одну команду на одноразовой БД (схема 036, роль NOBYPASSRLS, 37 таблиц FORCE RLS); tamper-цикл красный в обе стороны. Подтверждено на раннере прогоном 33006795900: behavioral 470 passed — ровно столько же, сколько до правки, ни один тест не потерян и не ослаблен.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1452,21 +1460,21 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Зафиксировать approved personas/retailer-scope</t>
+          <t>Strict RLS context по умолчанию</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-001</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1475,34 +1483,30 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>mini-design/ADR: persona→permissions→scope [owner]</t>
+          <t>admin elevation только setup [behavioral: `tests/behavioral/conftest.py::strict get_db default`]</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · behavioral · RUN_BEHAVIORAL_TESTS=1 python3 -m pytest tests/behavioral -q; verified · behavioral · tamper — маска возвращена, хук фазы убран, запись allowlist без дефекта; verified · ci_run · gh run 33015298420 — Behavioral PostgreSQL Tests success на 1e7a2bf; verified · artifact · docs/architecture/rm-stab-002-strict-rls-context-design-gate.md</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2); закрывает мою находку BEHAVIORAL-ADMIN-MASK-001. Элевация привязана к фазе прогона. Замер: на маске держались 181 из 470 тестов — 148 setup, 13 teardown, 20 тел. Вскрыт продовый дефект на двух device-маршрутах, по решению владельца вынесен в RM-TECH-210. Подтверждено на раннере прогоном 33015298420: behavioral 475 passed (470 прежних + 5 новых пинов), release-gate success.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-STAB-003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1512,21 +1516,21 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Реализовать approved RBAC/RLS scope</t>
+          <t>Зафиксировать approved personas/retailer-scope</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003, RM-STAB-006</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1540,12 +1544,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>migration_application</t>
+          <t>scope_decision</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>API/portal/migration согласованы [behavioral: `tests/behavioral/test_retailer_scope_rbac.py`]</t>
+          <t>mini-design/ADR: persona→permissions→scope [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-035/DEC-023)`]</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1555,14 +1559,14 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-005</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1577,16 +1581,16 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Исправить C1 UI-smoke и расширить общий guard</t>
+          <t>Реализовать approved RBAC/RLS scope</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-STAB-003, RM-STAB-006</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1598,10 +1602,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>нет API/deep goto/sleep/broad retry [command: `UI_SMOKE_RUN=1 python3 -m pytest tests/ui-contract -q`]</t>
+          <t>API/portal/migration согласованы [behavioral: `tests/behavioral/test_retailer_scope_rbac.py`]</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1618,7 +1626,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-006</t>
+          <t>RM-STAB-005</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1628,21 +1636,21 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Нормативный формат всех UI journeys registry</t>
+          <t>Исправить C1 UI-smoke и расширить общий guard</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-003</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1665,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>validator: actor, permission, entry, `Happy-path: N`, selectors, negative expectation [command: `python3 scripts/ci/check-journey-spec.py --strict`]; число journeys вычисляется из feature-registry, не фиксируется в задаче (RM-GOV-009 - «45/45» не подтверждено r421) [command: `python3 scripts/roadmap-consistency-check.py`]</t>
+          <t>нет API/deep goto/sleep/broad retry [command: `UI_SMOKE_RUN=1 python3 -m pytest tests/ui-contract -q`]</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1674,7 +1682,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-007</t>
+          <t>RM-STAB-006</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1684,21 +1692,21 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>UI proof под intended roles</t>
+          <t>Нормативный формат всех UI journeys registry</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-STAB-003</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1713,7 +1721,7 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>critical journeys имеют positive intended-role и negative missing-permission proof [ui_smoke: `tests/ui-smoke/ci-subset.txt (intended-role variants)`]</t>
+          <t>validator: actor, permission, entry, `Happy-path: N`, selectors, negative expectation [command: `python3 scripts/ci/check-journey-spec.py --strict`]; число journeys вычисляется из feature-registry, не фиксируется в задаче (RM-GOV-009 - «45/45» не подтверждено r421) [command: `python3 scripts/roadmap-consistency-check.py`]</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1730,7 +1738,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-008</t>
+          <t>RM-STAB-007</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1745,16 +1753,16 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Единая blocking-политика UI-smoke</t>
+          <t>UI proof под intended roles</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-005, RM-STAB-007</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1766,14 +1774,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>canon_change</t>
-        </is>
-      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ordinary pytest отделён [ci_job: `release-gate`]</t>
+          <t>critical journeys имеют positive intended-role и negative missing-permission proof [ui_smoke: `tests/ui-smoke/ci-subset.txt (intended-role variants)`]</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1790,7 +1794,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-009</t>
+          <t>RM-STAB-008</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1805,16 +1809,16 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Воспроизводимые CI dependencies</t>
+          <t>Единая blocking-политика UI-smoke</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-STAB-005, RM-STAB-007</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1826,10 +1830,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>canon_change</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>CI ставит project lock/requirements [ci_job: `python-tests (installs from requirements.txt)`]</t>
+          <t>ordinary pytest отделён [ci_job: `release-gate`]</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1846,7 +1854,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-010</t>
+          <t>RM-STAB-009</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1856,12 +1864,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Зафиксировать signing gate</t>
+          <t>Воспроизводимые CI dependencies</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1885,7 +1893,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ADR/roadmap отражают §1.2 [artifact: `docs/architecture/adr/ADR-021-manifest-signing-gate.md`]</t>
+          <t>CI ставит project lock/requirements [ci_job: `python-tests (installs from requirements.txt)`]</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1895,14 +1903,14 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить alias DEC-003/OD-002, REQ-MAN-002/SEC-003</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-011</t>
+          <t>RM-STAB-010</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1917,16 +1925,16 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>W0 rebaseline</t>
+          <t>Зафиксировать signing gate</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-001, RM-STAB-002, RM-STAB-003, RM-STAB-004, RM-STAB-005, RM-STAB-006, RM-STAB-007, RM-STAB-008, RM-STAB-009, RM-STAB-010</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1941,7 +1949,7 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>named targeted → behavioral → UI subset → guards [command: `python3 scripts/ci/check-roadmap-schema.py --file docs/product/roadmap.yaml`]</t>
+          <t>ADR/roadmap отражают §1.2 [artifact: `docs/architecture/adr/ADR-021-manifest-signing-gate.md`]</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1951,14 +1959,14 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): STAND-001/002 перепривязать на RM-ENV-002 после ACCEPT</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить alias DEC-003/OD-002, REQ-MAN-002/SEC-003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-012</t>
+          <t>RM-STAB-011</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1968,21 +1976,21 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Async I/O boundary: детектор blocking I/O в async handlers (ADR-012)</t>
+          <t>W0 rebaseline</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-009</t>
+          <t>RM-STAB-001, RM-STAB-002, RM-STAB-003, RM-STAB-004, RM-STAB-005, RM-STAB-006, RM-STAB-007, RM-STAB-008, RM-STAB-009, RM-STAB-010</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1997,7 +2005,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>статический/рантайм-детектор красный на blocking I/O без threadpool; текущий код чист [command: `tests/test_api_tx_boundary.py`]</t>
+          <t>named targeted → behavioral → UI subset → guards [command: `python3 scripts/ci/check-roadmap-schema.py --file docs/product/roadmap.yaml`]</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2007,14 +2015,14 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-003; SC: SC-ARCH-005; DEC: -. Evidence: tests/test_api_tx_boundary.py; новый lint/pytest. Риск регрессии: средний: может вскрыть существующие blocking-вызовы.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): STAND-001/002 перепривязать на RM-ENV-002 после ACCEPT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-STAB-012</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2029,16 +2037,16 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>API attack protection: runtime negative suite (schema/size, IDOR, CSRF/XSS, SSRF, rate limit, headers, no secrets in logs)</t>
+          <t>Async I/O boundary: детектор blocking I/O в async handlers (ADR-012)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-009</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2061,7 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>каждый control имеет negative-тест: красный при отключении, зелёный при включении [behavioral: `tests/test_s065_rate_limit.py`]; 429 + Retry-After по endpoint и principal; audit rate-limit [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>статический/рантайм-детектор красный на blocking I/O без threadpool; текущий код чист [command: `tests/test_api_tx_boundary.py`]</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2063,14 +2071,14 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-006; SC: SC-SEC-004; DEC: -. Evidence: tests/test_s065_rate_limit.py; tests/test_phase3_security.py; новый negative suite. Риск регрессии: средний: ужесточение headers/CORS может сломать admin-web/advertiser-web.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-003; SC: SC-ARCH-005; DEC: -. Evidence: tests/test_api_tx_boundary.py; новый lint/pytest. Риск регрессии: средний: может вскрыть существующие blocking-вызовы.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-014</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2085,7 +2093,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Полнота аудита критичных действий и реальный actor (user/service/device)</t>
+          <t>API attack protection: runtime negative suite (schema/size, IDOR, CSRF/XSS, SSRF, rate limit, headers, no secrets in logs)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2109,7 +2117,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>реестр критичных действий ↔ audit events 100%; anonymous/подставной actor отклонён [behavioral: `tests/behavioral/test_rm_stab_014.py`]</t>
+          <t>каждый control имеет negative-тест: красный при отключении, зелёный при включении [behavioral: `tests/test_s065_rate_limit.py`]; 429 + Retry-After по endpoint и principal; audit rate-limit [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2119,14 +2127,14 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-005; SC: SC-SEC-003; DEC: -. Evidence: tests/ui-smoke/test_uismoke__audit__view.py; новый behavioral. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-006; SC: SC-SEC-004; DEC: -. Evidence: tests/test_s065_rate_limit.py; tests/test_phase3_security.py; новый negative suite. Риск регрессии: средний: ужесточение headers/CORS может сломать admin-web/advertiser-web.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-015</t>
+          <t>RM-STAB-014</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2141,16 +2149,16 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Control plane системного администратора: отдельные permission-коды и scope</t>
+          <t>Полнота аудита критичных действий и реальный actor (user/service/device)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2165,7 +2173,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>users/roles/devices/settings/monitoring/audit — отдельные коды; approved campaign без отдельного права не меняется [behavioral: `tests/test_phase3_user_management.py`]</t>
+          <t>реестр критичных действий ↔ audit events 100%; anonymous/подставной actor отклонён [behavioral: `tests/behavioral/test_rm_stab_014.py`]</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2175,14 +2183,14 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-005; SC: SC-SEC-003; DEC: -. Evidence: tests/ui-smoke/test_uismoke__audit__view.py; новый behavioral. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-016</t>
+          <t>RM-STAB-015</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2197,16 +2205,16 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Object storage boundary: приватные buckets, presigned TTL, ограниченные service accounts</t>
+          <t>Control plane системного администратора: отдельные permission-коды и scope</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>RM-ENV-001</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2221,7 +2229,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>анонимный доступ запрещён; просроченный presigned URL отклонён [behavioral: `tests/test_storage_service.py`]</t>
+          <t>users/roles/devices/settings/monitoring/audit — отдельные коды; approved campaign без отдельного права не меняется [behavioral: `tests/test_phase3_user_management.py`]</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2231,14 +2239,14 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-007; SC: SC-SEC-005; DEC: -. Evidence: tests/test_storage_service.py; tests/integration/test_minio_upload.py. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-017</t>
+          <t>RM-STAB-016</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2253,16 +2261,16 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Независимость production от внешнего runtime: production smoke при выключенных dashboard/LLM-агентах</t>
+          <t>Object storage boundary: приватные buckets, presigned TTL, ограниченные service accounts</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-009</t>
+          <t>RM-ENV-001</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2277,7 +2285,7 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>полный production smoke проходит без внешних наблюдателей; ни один сервис не вызывает внешний runtime (egress allow-list) [command: `tests/test_production_config_gate.py`]</t>
+          <t>анонимный доступ запрещён; просроченный presigned URL отклонён [behavioral: `tests/test_storage_service.py`]</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2287,14 +2295,14 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-002; SC: SC-ARCH-004; DEC: DEC-014. Evidence: tests/test_production_config_gate.py; egress check. Риск регрессии: низкий. monitoring-dashboard — read-only наблюдатель (OD-027), не зависимость.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-007; SC: SC-SEC-005; DEC: -. Evidence: tests/test_storage_service.py; tests/integration/test_minio_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210</t>
+          <t>RM-STAB-017</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2309,16 +2317,16 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>RLS-контекст на device-маршрутах онбординга</t>
+          <t>Независимость production от внешнего runtime: production smoke при выключенных dashboard/LLM-агентах</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-002</t>
+          <t>RM-STAB-009</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2330,14 +2338,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; прямой запрос к БД под ролью приложения без контекста находит активный код онбординга [behavioral: `tests/behavioral/test_rls_context_strictness.py`]</t>
+          <t>полный production smoke проходит без внешних наблюдателей; ни один сервис не вызывает внешний runtime (egress allow-list) [command: `tests/test_production_config_gate.py`]</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2347,19 +2351,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-002; SC: SC-ARCH-004; DEC: DEC-014. Evidence: tests/test_production_config_gate.py; egress check. Риск регрессии: низкий. monitoring-dashboard — read-only наблюдатель (OD-027), не зависимость.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2369,16 +2373,16 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
+          <t>RLS-контекст на device-маршрутах онбординга</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-STAB-002</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -2390,10 +2394,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; прямой запрос к БД под ролью приложения без контекста находит активный код онбординга [behavioral: `tests/behavioral/test_rls_context_strictness.py`]</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2403,14 +2411,14 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-221</t>
+          <t>RM-OPS-005</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2420,21 +2428,21 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
+          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2443,13 +2451,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
+          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2459,14 +2471,14 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2476,21 +2488,21 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
+          <t>SLO objectives и измерение</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2505,7 +2517,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2515,14 +2527,14 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-223</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2537,16 +2549,16 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
+          <t>OpenAPI + event/manifest JSON Schema (AG): as-built генерация + target из §26/AB, contract tests</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2558,14 +2570,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
+          <t>OpenAPI/event schemas версионированы, examples и deprecation policy; contract tests зелёные [command: `python3 scripts/ci/roadmap-governance-guard.py`]; одна canonical opaque идентификация на версию API; alias {id} с deprecation date [behavioral: `tests/behavioral/test_rm_tech_220.py`]</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2575,14 +2583,14 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-221</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2597,7 +2605,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
+          <t>Разделение User/Device/analytics/emergency API; device client не достигает admin</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2618,14 +2626,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
+          <t>device JWT → admin endpoint = 403 на всех admin-роутах [behavioral: `tests/test_phase3_protected_identity.py`]</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2635,14 +2639,14 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-002; SC: SC-API-002; DEC: -. Evidence: tests/test_phase3_protected_identity.py; новый negative. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2657,16 +2661,16 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
+          <t>Канонический POST /api/v1/pop/batch, legacy /device/pop/batch как alias с deprecation</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-222</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2685,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
+          <t>ответы канонического и legacy идентичны; deprecation header; batch&gt;500 → 422; чужой device_id отклонён [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2691,14 +2695,14 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-API-003, REQ-POP-003; SC: SC-API-003, SC-POP-003; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_edge002fu_real_endpoint.py. Риск регрессии: средний: runtime/плеер использует legacy path.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-226</t>
+          <t>RM-TECH-223</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2713,16 +2717,16 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
+          <t>Manifest field contract и ACK-состояния runtime (opaque media_ref, no MinIO keys)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2736,12 +2740,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>migration_application</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
+          <t>все обязательные поля §25 REQ-MAN-004 в schema; внутренний object key не раскрыт; 6 ACK states принимаются [behavioral: `tests/test_contract_manifest.py`]</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2751,14 +2755,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-MAN-004; SC: SC-MAN-001; DEC: -. Evidence: tests/test_contract_manifest.py; tests/behavioral/test_edge002_manifest_delivery.py. Риск регрессии: высокий: меняет device-facing контракт — owner gate device_contract.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-227</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2773,16 +2777,16 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
+          <t>Heartbeat contract POST /api/v1/device/heartbeat: дедуп, scope, clock drift, freshness thresholds</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-225</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2794,10 +2798,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
+          <t>валидный/повтор/чужой scope/просроченный heartbeat дают ожидаемые результаты; legacy alias с той же семантикой [behavioral: `tests/behavioral/test_edge004_heartbeat.py`]</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2807,14 +2815,14 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-009; SC: SC-OPS-002; DEC: -. Evidence: tests/behavioral/test_edge004_heartbeat.py. Риск регрессии: высокий: device-facing.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-228</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2829,12 +2837,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
+          <t>PoP duplicate semantics по OD-019: 200 + per-event duplicate/409, amendment ADR-017</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-222</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -2853,7 +2861,7 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
+          <t>ADR-017 amendment принят; behavioral: повтор batch → per-event duplicate, summary не удвоен, порядок хронологический [behavioral: `tests/behavioral/test_edge003_pop_ingestion.py`]</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2863,14 +2871,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-002; SC: SC-POP-002; DEC: DEC-024. Evidence: tests/behavioral/test_edge003_pop_ingestion.py; ADR-017 amendment. Риск регрессии: низкий: закрепляет текущее поведение.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-226</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2880,21 +2888,21 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
+          <t>Proof model: pop_mode error/not_applied — schema/runtime migration из compatibility projection</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2906,10 +2914,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
+          <t>ProofMode содержит 9 значений; отчёт не смешивает playback/apply/delivery/error [behavioral: `tests/behavioral/test_pop_schema.py`]</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2919,14 +2931,14 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-001; SC: SC-POP-001; DEC: -. Evidence: tests/behavioral/test_pop_schema.py; migration. Риск регрессии: средний: enum migration + отчёты.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-230</t>
+          <t>RM-TECH-227</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2936,21 +2948,21 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
+          <t>Валидация proof_event_v1: playback_result/failure_reason, clock-drift quarantine, no internal IDs/PII</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-225</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2965,7 +2977,7 @@
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
+          <t>недопустимый playback_result/внутренний ID/сдвиг часов → 422 или quarantine; SHA/signature проверены [behavioral: `tests/test_contract_pop.py`]</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2975,38 +2987,38 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-POP-004; SC: SC-POP-004; DEC: -. Evidence: tests/test_contract_pop.py; tests/behavioral/test_pop_schema.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-228</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Записать managed-first scope</t>
+          <t>Окно совместимости device/API/manifest: heartbeat объявляет версии, сервер выбирает представление</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3021,7 +3033,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
+          <t>совместимая версия выбрана по объявленным capabilities; breaking change без staged rollout отклонён contract-тестом [behavioral: `tests/test_version_identity.py`]</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3031,19 +3043,19 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-003; SC: SC-NFR-003; DEC: -. Evidence: tests/test_version_identity.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3053,16 +3065,16 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Таксономия причин недопоказа</t>
+          <t>ERD + data dictionary + migration plan (AG): инвентарь сущностей §15, retailer_id NOT NULL + двухуровневый RLS</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3077,7 +3089,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
+          <t>as-built ERD из моделей; каждая группа §15 присутствует или имеет migration task; tenant-таблицы с retailer_id+FK+RLS [artifact: `tests/behavioral/test_adr018_multitenancy_rls.py`]; behavioral RLS proof под ролью приложения NOBYPASSRLS [behavioral: `tests/behavioral/test_adr018_multitenancy_rls.py`]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3087,34 +3099,34 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Вытеснение и объяснимые приоритеты</t>
+          <t>Channel Adapter contract (design-only до второго канала): versioned task, receipt, proof/ack, error, health, mock mode</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3133,7 +3145,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
+          <t>contract spec + JSON Schema без реализации adapter/mock (ADR-019) [artifact: `docs/architecture contract`]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3143,34 +3155,34 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-006; SC: SC-ORCH-005; DEC: -. Evidence: docs/architecture contract; schema. Риск регрессии: низкий: только документ.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-203</t>
+          <t>RM-TECH-231</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Overbooking policy</t>
+          <t>channel-capability-matrix.yaml (AG) для первого канала KSO: channel/surface/rendition/proof/SLA/vendor constraints</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202</t>
+          <t>RM-TECH-230</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3186,10 +3198,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
+          <t>матрица покрывает KSO channel/surface/rendition/proof/SLA/vendor constraints; каждая строка ссылается на REQ-CHAN-*/REQ-MAN-*/REQ-POP-* [artifact: `docs/product/channel-capability-matrix.yaml`]; артефакт принят владельцем как часть handoff-пакета AG [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3199,38 +3215,38 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-253</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Creative QA без неутверждённого HTML5</t>
+          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3245,7 +3261,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
+          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3255,38 +3271,38 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено CORE → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206</t>
+          <t>RM-TECH-288</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>License renewal/grant boundary</t>
+          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3301,7 +3317,7 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
+          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3311,38 +3327,38 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>RM-UX-011</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
+          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-STAB-004, RM-STAB-006</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3354,14 +3370,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
+          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3371,14 +3383,14 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-241</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3388,21 +3400,21 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
+          <t>Записать managed-first scope</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3417,7 +3429,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
+          <t>roadmap явно исключает `self.campaign_create` из ближайшего control-plane pilot [artifact: `docs/product/roadmap.yaml (pilot scope)`]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3427,14 +3439,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): ссылки OD-005/DEC-011, REQ-SCOPE-001</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3444,21 +3456,21 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
+          <t>Таксономия причин недопоказа</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-240</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3473,7 +3485,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
+          <t>8 категорий ТЗ, source/report/history contract и owner-approved artifact [artifact: `docs/product/underdelivery-reason-taxonomy.yaml`]</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3483,14 +3495,14 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3505,16 +3517,16 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
+          <t>Вытеснение и объяснимые приоритеты</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-242</t>
+          <t>RM-TECH-201</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3541,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
+          <t>versioned rules [behavioral: `tests/behavioral/test_campaign_preemption.py`]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3539,14 +3551,14 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-007 и порядок приоритета §12; исключение §3.1 (OD-018) — единственная точка изменения engine → RM-TECH-285 зависит от неё</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-244</t>
+          <t>RM-TECH-203</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3561,16 +3573,16 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
+          <t>Overbooking policy</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-243</t>
+          <t>RM-TECH-202</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3585,7 +3597,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
+          <t>default deny [behavioral: `tests/behavioral/test_inventory_overbooking_policy.py`]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3595,14 +3607,14 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3617,16 +3629,16 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
+          <t>Creative QA без неутверждённого HTML5</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3638,14 +3650,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
+          <t>metadata/antivirus/executable deny и immutable QA result [behavioral: `tests/behavioral/test_creative_qa.py`]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3655,14 +3663,14 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-206</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3677,16 +3685,16 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
+          <t>License renewal/grant boundary</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3701,7 +3709,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
+          <t>атомарная семантика §1.6 [behavioral: `tests/behavioral/test_license_renewal_boundary.py`]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3711,14 +3719,14 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-247</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3733,16 +3741,16 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
+          <t>Универсальная иерархия носителей: migration + seed network/branch/cluster/store/store_group/channel/device/surface</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3754,10 +3762,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
+          <t>все уровни существуют с FK и RLS; seed заполняет иерархию; чужой scope не видит [behavioral: `tests/behavioral/test_scope_rls.py`]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3767,14 +3779,14 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-001; SC: SC-DATA-001; DEC: -. Evidence: migration; tests/behavioral/test_scope_rls.py. Риск регрессии: высокий: схема ядра.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-241</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3789,16 +3801,16 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
+          <t>Target resolution boundary: broad target → display_surface_id, запрет physical_device_id как target</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-245</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3813,7 +3825,7 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
+          <t>планирование разрешает target до surface; physical_device_id в target отклоняется [behavioral: `tests/test_s089_inventory_simulation.py`]</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3823,14 +3835,14 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CORE-003; SC: SC-ARCH-002; DEC: -. Evidence: tests/test_s089_inventory_simulation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3845,16 +3857,16 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
+          <t>Outbox для любой OLTP-записи с domain event; revocation/refresh manifest при pause/archive/expiry</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-248</t>
+          <t>RM-TECH-240</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3881,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
+          <t>каждая доменная мутация создаёт outbox event в той же транзакции; pause/archive порождают revocation [behavioral: `tests/behavioral/test_outbox.py`]</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3879,14 +3891,14 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-003; SC: SC-ORCH-002; DEC: -. Evidence: tests/behavioral/test_outbox.py. Риск регрессии: средний: транзакционные границы всех сервисов.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3901,16 +3913,16 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
+          <t>Outbox relay: lease/publishing, Nats-Msg-Id, 7 попыток → dead_letter, partition order, DLQ policy, no PII</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-204</t>
+          <t>RM-TECH-242</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3922,14 +3934,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>migration_application</t>
-        </is>
-      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
+          <t>7 отказов брокера → dead_letter с operator action; ack → published; replay идемпотентен [behavioral: `tests/behavioral/test_outbox_relay.py`]; NATS recovery integration зелёный [command: `tests/behavioral/test_outbox_relay.py`]</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3939,14 +3947,14 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-004; SC: SC-ORCH-003; DEC: DEC-004. Evidence: tests/behavioral/test_outbox_relay.py; tests/integration/test_nats_recovery.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-251</t>
+          <t>RM-TECH-244</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3961,16 +3969,16 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
+          <t>Adapter task lifecycle через persisted queue (event-driven массовая публикация)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-243</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3985,7 +3993,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
+          <t>активация на 1000 устройств не ждёт устройств; задачи агрегируют статусы [behavioral: `tests/behavioral/test_delivery_foundation.py`]</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3995,14 +4003,14 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ORCH-002; SC: SC-ORCH-006; DEC: DEC-004. Evidence: tests/behavioral/test_delivery_foundation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-252</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4017,7 +4025,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
+          <t>Campaign lifecycle по ADR-015/OD-036: scheduled, resume, revise, archive; единый guard и audit</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4040,12 +4048,12 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>protected_boundary</t>
+          <t>migration_application</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
+          <t>_CAMPAIGN_TRANSITIONS = ADR-015; каждый переход через guard с audit; возврат в draft создаёт revision [behavioral: `tests/behavioral/test_campaign_domain.py`]; campaign.* smokes зелёные после изменения [ui_smoke: `tests/ui-smoke/test_rm_tech_245.py`]</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4055,14 +4063,14 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-010; SC: -; DEC: DEC-025. Evidence: tests/behavioral/test_campaign_domain.py; tests/ui-smoke/test_uismoke__campaign__*.py. Риск регрессии: высокий: меняет runtime enum кампании и UI.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4072,21 +4080,21 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Data protection: data classes, lawful purpose, минимизация PII, residency; retention по OD-009</t>
+          <t>Commerce order: отмена по OD-020 (draft→cancelled, confirmed — reversal), payment projection отдельно</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4101,7 +4109,7 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>реестр data classes для всех сущностей; новая PII-сущность без класса — красный design-gate [artifact: `docs/architecture data classes`]</t>
+          <t>_ORDER_TRANSITIONS: draft→cancelled разрешён, confirmed→cancelled запрещён, reversal с audit [behavioral: `tests/test_commerce_a2.py`]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4111,14 +4119,14 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: docs/architecture data classes. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-014; SC: -; DEC: DEC-017, DEC-026. Evidence: tests/test_commerce_a2.py; tests/behavioral/test_commerce_rls.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-254</t>
+          <t>RM-TECH-247</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4133,7 +4141,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
+          <t>Approval policy: required roles/scope/порядок/timeout per campaign/placement/creative</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4157,7 +4165,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
+          <t>политика версионирована; submit/approve соблюдают порядок и timeout; negative для чужого scope [behavioral: `tests/behavioral/test_campaign_approval.py`]</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4167,14 +4175,14 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-003; SC: -; DEC: -. Evidence: tests/behavioral/test_campaign_approval.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-255</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4189,16 +4197,16 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
+          <t>Flight/placement windows: versioned start_at/end_at UTC, проверка при simulation/manifest/runtime</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-224</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4213,7 +4221,7 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
+          <t>показ вне окна запрещён на трёх уровнях; DST/праздники/closed stores — версионированные правила [behavioral: `tests/test_s063_pop_timezone.py`]</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4223,19 +4231,19 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-005, REQ-NFR-002; SC: SC-NFR-002; DEC: -. Evidence: tests/test_s063_pop_timezone.py; новый behavioral. Риск регрессии: высокий: расписание доставки.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-002</t>
+          <t>RM-TECH-249</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4245,16 +4253,16 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>`self.campaign_create` в будущей ветке</t>
+          <t>Manifest eligibility: approved status + валидный flight/contract + resolved target + readiness</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-001</t>
+          <t>RM-TECH-248</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4263,17 +4271,13 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
+          <t>неэлигибельная кампания не попадает в manifest; причина объяснима [behavioral: `tests/behavioral/test_delivery_generation.py`]</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4283,19 +4287,19 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-006; SC: -; DEC: -. Evidence: tests/behavioral/test_delivery_generation.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4305,16 +4309,16 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Accessibility оставшихся форм + route matrix (A3)</t>
+          <t>Creative/rendition state machine и immutable media history (uploaded→scanning→qa_failed/approved→superseded→retained)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-204</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4326,10 +4330,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>migration_application</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
+          <t>каждая версия хранит uploader/SHA-256/QA-решение/связь; закрытый отчёт воспроизводим после logical delete [behavioral: `tests/behavioral/test_creative_assets.py`]</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4339,19 +4347,19 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CONT-002; SC: SC-DATA-002; DEC: -. Evidence: tests/behavioral/test_creative_assets.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4361,16 +4369,16 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Поиск/сортировка/усечение таблиц (A2)</t>
+          <t>Data ownership/lineage: immutable versioning и diff campaign/placement/playlist, словарь владельцев</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4385,7 +4393,7 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
+          <t>сохранение создаёт версию с diff и actor; предыдущая неизменяема [behavioral: `tests/behavioral/test_rm_tech_251.py`]</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4395,19 +4403,19 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-001; SC: SC-DATA-004; DEC: DEC-007. Evidence: новый behavioral. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-TECH-252</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4417,16 +4425,16 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Responsive-проверка (A4)</t>
+          <t>Identity: AD/LDAP или SSO для internal staff, MFA до production (OD-008)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-002</t>
+          <t>RM-STAB-004</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4438,10 +4446,14 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
+          <t>логин через IdP; production-профиль без MFA отклоняет; TLS-профиль зафиксирован [behavioral: `tests/test_phase3_auth_api.py`]</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4451,19 +4463,19 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-001; SC: SC-SEC-008; DEC: -. Evidence: tests/test_phase3_auth_api.py; tests/behavioral/test_auth_dual_e2e.py. Риск регрессии: высокий: вход всех пользователей.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-TECH-254</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4473,16 +4485,16 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Согласованность состояний и терминов (A6)</t>
+          <t>Emergency state machine: requested→authorized→dispatching→applied→resuming→closed, MFA+reason, приоритетный канал</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-003</t>
+          <t>RM-TECH-245</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4497,7 +4509,7 @@
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
+          <t>emergency с причиной; per-target result; audit actor/reason/affected; resume возвращает штатный manifest [behavioral: `tests/test_phase3_emergency_api.py`]; emergency.* smokes зелёные [ui_smoke: `tests/ui-smoke/test_uismoke__emergency__activate.py`]</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4507,19 +4519,19 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-007; SC: SC-OPS-003; DEC: -. Evidence: tests/test_phase3_emergency_api.py; tests/ui-smoke/test_uismoke__emergency__activate.py. Риск регрессии: высокий: аварийный контур.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-TECH-255</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4529,16 +4541,16 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Adoption доказанных primitives малыми slices (A1b)</t>
+          <t>Device health/commands: пороги статусов по профилю, per-device view, команды с подтверждением</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-004</t>
+          <t>RM-TECH-224</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4553,7 +4565,7 @@
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
+          <t>online→degraded→offline по порогам; команда доставлена и подтверждена [behavioral: `tests/behavioral/test_rm_tech_255.py`]; device.health_view smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__device__health_view.py`]</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4563,14 +4575,14 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-001; SC: SC-OPS-006; DEC: -. Evidence: tests/ui-smoke/test_uismoke__device__health_view.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-006</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4585,16 +4597,16 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Advertiser-web UX audit/fixes (A5)</t>
+          <t>`self.campaign_create` в будущей ветке</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-005</t>
+          <t>RM-BIZ-001</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4603,13 +4615,17 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
+          <t>mini-design, journey, backend/UI/RLS, intended-role smoke, walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__campaign_create.py`]</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4619,14 +4635,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2). RM-GOV-009 (OD-037): blocked до OD-013 — полный self-service вне pilot scope (REQ-V26-003, OD-005)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-007</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4636,21 +4652,21 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Human operator walkthrough (A7)</t>
+          <t>Accessibility оставшихся форм + route matrix (A3)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4665,7 +4681,7 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>человек проходит exact stand bundle [human]</t>
+          <t>labels/ARIA/axe/targeted vitest [artifact: `docs/product/ux-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4682,7 +4698,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-008</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4697,16 +4713,16 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
+          <t>Поиск/сортировка/усечение таблиц (A2)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-249, RM-UX-004</t>
+          <t>RM-UX-001</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4721,7 +4737,7 @@
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
+          <t>server semantics для pagination [ui_smoke: `tests/ui-smoke/test_uismoke__campaign__create.py`]</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4731,14 +4747,14 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-009</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4753,12 +4769,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
+          <t>Responsive-проверка (A4)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-250</t>
+          <t>RM-UX-002</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
@@ -4777,7 +4793,7 @@
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
+          <t>все routes из `ux-route-matrix.yaml` проверены на 390px без overflow/crop [artifact: `docs/product/ux-responsive-report.yaml`]</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4787,14 +4803,14 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-011</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4804,21 +4820,21 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>role-scope-matrix.yaml + portal-route-matrix.yaml + journeys/ (AG) из seed/pg_policies/registry</t>
+          <t>Согласованность состояний и терминов (A6)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-004, RM-STAB-006</t>
+          <t>RM-UX-003</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4849,7 @@
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>матрицы генерируются и сверяются guard; deny-cases покрыты behavioral [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>route matrix покрывает empty/loading/error/403/success и locale-key check [artifact: `docs/product/ux-route-matrix.yaml (states coverage)`]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4843,38 +4859,38 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>KSO environment + player/playlist design</t>
+          <t>Adoption доказанных primitives малыми slices (A1b)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-UX-004</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4886,14 +4902,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
+          <t>каждый slice имеет отдельный diff/test/review [ci_job: `frontend`]</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4903,19 +4915,19 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-UX-006</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4925,16 +4937,16 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>KSO player/playlist/PoP chain</t>
+          <t>Advertiser-web UX audit/fixes (A5)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207A</t>
+          <t>RM-UX-005</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4946,14 +4958,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
+          <t>versioned `docs/product/advertiser-route-matrix.yaml` с точным списком 15 routes [artifact: `docs/product/advertiser-route-matrix.yaml`]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4970,31 +4978,31 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-UX-007</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Signed licensing Layer 2</t>
+          <t>Human operator walkthrough (A7)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
+          <t>RM-UX-001, RM-UX-002, RM-UX-003, RM-UX-004, RM-UX-005, RM-UX-006</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5006,14 +5014,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>protected_boundary</t>
-        </is>
-      </c>
+      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
+          <t>человек проходит exact stand bundle [human: `PROJECT_STATE.md строка `operator walkthrough` (AGENTS.md правило 8); сценарии docs/product/operator-walkthrough-dev.md`]</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5023,19 +5027,19 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) ПРИОСТАНОВЛЕНО владельцем 2026-08-31 (OD-041) до выравнивания ТЗ/roadmap/gates и утверждения единого плана реализации; не закрывать, done не ставить.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-260</t>
+          <t>RM-UX-008</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5045,16 +5049,16 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
+          <t>Campaign readiness matrix по каналам (rendition/inventory/conflicts/forecast/PoP mode/SLA) с действием на blocked</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-249, RM-UX-004</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5066,14 +5070,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>device_contract</t>
-        </is>
-      </c>
+      <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
+          <t>экран согласования показывает матрицу; каждый blocked/warning ведёт к действию [ui_smoke: `tests/ui-smoke/test_rm_ux_008.py`]</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5083,34 +5083,34 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-004; SC: SC-UX-002; DEC: -. Evidence: новый ui-smoke; vitest. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-261</t>
+          <t>RM-UX-009</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
+          <t>Договор рекламодателя: immutable file versions, server-side SHA-256, legal status (юр. решение)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B, RM-TECH-230</t>
+          <t>RM-TECH-250</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -5123,17 +5123,13 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
+          <t>повторная загрузка создаёт новую версию, SHA проверен сервером; старая версия неизменяема [behavioral: `tests/test_advertiser_contracts.py`]; advertiser.contract_crud smoke зелёный [ui_smoke: `tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py`]</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5143,14 +5139,14 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-017; SC: -; DEC: -. Evidence: tests/test_advertiser_contracts.py; tests/ui-smoke/test_uismoke__advertiser__contract_pdf_upload.py. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-262</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5160,21 +5156,21 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
+          <t>KSO environment + player/playlist design</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-261</t>
+          <t>Gate-S</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5183,13 +5179,17 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
+          <t>versioned environment audit, import/contract mini-design и test plan [artifact: `docs/architecture/kso-environment-audit.md`]</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. blocked: ложная ESL-посылка, master adapter (OD-023).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-STAND-003 feasibility gate явно в acceptance; ADR-019/OD-022</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5221,16 +5221,16 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
+          <t>KSO player/playlist/PoP chain</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-210, RM-TECH-255</t>
+          <t>RM-TECH-207A</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5239,13 +5239,17 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>device_contract</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
+          <t>contract tests и playback→manifest→PoP behavioral proof [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; Playlist entity и state machine §6 ТЗ (draft → validating → valid/invalid → approved → published → superseded/rolled_back); published immutable [behavioral: `tests/behavioral/test_kso_playback_chain.py`]; manifest target lifecycle (generated → signed → queued → delivered → applied/failed/expired) и canonical POST /api/v1/pop/batch [behavioral: `tests/behavioral/test_kso_playback_chain.py`]</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5255,14 +5259,14 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. blocked RM-TECH-210.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-264</t>
+          <t>RM-TECH-208</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5277,16 +5281,16 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
+          <t>Signed licensing Layer 2</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-206, RM-TECH-207B, RM-STAB-010</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5295,13 +5299,17 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>protected_boundary</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
+          <t>Ed25519 offline verify, kid/rotation/revocation, UI, tamper/rollback [behavioral: `tests/behavioral/test_signed_license_layer2.py`]</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5311,14 +5319,14 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. blocked OD-023.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-260</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5328,17 +5336,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
+          <t>Runtime cache lifecycle: лимит по профилю, детерминированная очистка, last-known-good</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-229</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -5351,17 +5359,17 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>scope_decision</t>
+          <t>device_contract</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
+          <t>кэш на лимите: очистка по правилу; last-known-good сохранён; просроченная реклама не показывается [behavioral: `tests/behavioral/test_rm_tech_260.py`]</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5371,34 +5379,34 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; blocked до имени владельца.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-008; SC: SC-EDGE-002; DEC: -. Evidence: runtime simulator tests. Риск регрессии: средний: плеер.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-261</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>`self.report_view` plan/fact</t>
+          <t>Второй канал: решение OD-021 + channel-capability-matrix.yaml (AG); extraction design по ADR-019</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-201, RM-TECH-207B</t>
+          <t>RM-TECH-207B, RM-TECH-230</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -5411,13 +5419,17 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
+          <t>владелец назвал канал и владельца (OD-021); матрица возможностей утверждена [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; extraction design: KSO-вертикаль как первый adapter без поломки контрактов [artifact: `docs/audit/RM-TECH-261-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5427,38 +5439,38 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-CHAN-001, REQ-ORCH-005; SC: SC-CHAN-002, SC-ORCH-004; DEC: DEC-001, DEC-002. Evidence: OD-021; design doc. Риск регрессии: высокий: рефакторинг KSO-вертикали. blocked до OD-021; Orchestrator/Adapter Layer/mock не создаются раньше (ADR-019/OD-022).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-262</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>SLO objectives и измерение</t>
+          <t>Dynamic creative binding/rendition safety (V26-008) на одном канале</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Gate-S</t>
+          <t>RM-TECH-280, RM-TECH-261</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5473,7 +5485,7 @@
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>каждое число ТЗ имеет formula/window/owner/metric либо `not measurable` [artifact: `docs/product/slo-objectives.yaml`]</t>
+          <t>master-confirmed price/promo подставляется при manifest generation; SLA-тест dynamic manifest [behavioral: `tests/behavioral/test_rm_tech_262.py`]</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5483,38 +5495,38 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-008; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. ложная ESL-посылка снимается prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-209</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>ClickHouse capacity trigger</t>
+          <t>Field mobile operations: scoped mobile web для сотрудника магазина (устройства, фото, инциденты)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-207B</t>
+          <t>RM-TECH-210, RM-TECH-255</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5529,7 +5541,7 @@
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
+          <t>journey field_ops.device_confirm под ролью магазина с RLS; negative чужой магазин [ui_smoke: `tests/ui-smoke/test_rm_tech_263.py`]</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5539,38 +5551,38 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-009; SC: -; DEC: -. Evidence: new ui-smoke. Риск регрессии: средний. prerequisite RM-TECH-210 (RLS device) - planned по зависимости; feature field_ops.device_confirm blocked до задачи (RM-GOV-012 выравнивание: blocked = решение владельца/внешний факт, а не зависимость).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-264</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
+          <t>ESL/price-checker: интеграция только через approved price/SKU master (INT-002)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5582,14 +5594,10 @@
           <t>planned</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>price-related данные приходят из master или проходят reconciliation; расхождение блокирует показ [behavioral: `tests/behavioral/test_rm_tech_264.py`]</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5599,38 +5607,38 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: new behavioral. Риск регрессии: высокий. OD-023 approved 2026-08-31 - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
+          <t>Prerequisite: master-data adapter цен/SKU (контракт, owner OD-023, reconciliation)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280</t>
+          <t>RM-TECH-229</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5639,13 +5647,17 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
+          <t>владелец master-данных назначен (OD-023 approved); contract + reconciliation design утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]; adapter в mock/test mode проходит contract tests [behavioral: `tests/behavioral/test_rm_tech_280.py`]</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5655,14 +5667,14 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. blocked RM-TECH-280.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-002; SC: -; DEC: DEC-005. Evidence: OD-023; contract tests. Риск регрессии: средний. отсутствующий prerequisite по AQ.1 №5; OD-023 approved 2026-08-31 (роль Product Data Owner) - planned; owner gate: контракт/scope adapter.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5677,16 +5689,16 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
+          <t>`self.report_view` plan/fact</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281, RM-TECH-229</t>
+          <t>RM-TECH-201, RM-TECH-207B</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5695,13 +5707,13 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
+          <t>реальные PoP/причины/RLS, journey/smoke/walkthrough [ui_smoke: `tests/ui-smoke/test_uismoke__self__report_view.py`]</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5711,14 +5723,14 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-BIZ-011; зависит от RM-TECH-207B (реальные PoP) — без изменений</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-209</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5728,21 +5740,21 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
+          <t>ClickHouse capacity trigger</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-280, RM-TECH-253</t>
+          <t>RM-TECH-207B</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5751,17 +5763,13 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>измеряемый PoP rate/retention threshold и owner migration gate [artifact: `docs/product/clickhouse-capacity-trigger.yaml`]</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5771,14 +5779,14 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-284</t>
+          <t>RM-TECH-256</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5788,21 +5796,21 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
+          <t>Business outcome KPI: baseline/target/metric definition для целей §1.2 (OD-024 exit criteria)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-282</t>
+          <t>RM-TECH-205</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5811,13 +5819,17 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
+          <t>каждая бизнес-цель имеет baseline/target/формулу/владельца, утверждено владельцем [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5827,14 +5839,14 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-013; SC: -; DEC: DEC-010. Evidence: artifact kpi register. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-TECH-281</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5849,12 +5861,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
+          <t>Prerequisite: sales-reference ingestion (агрегаты store/SKU/day) + методология baseline/test-control</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-202, RM-TECH-280</t>
+          <t>RM-TECH-280</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
@@ -5867,13 +5879,13 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
+          <t>пакетная загрузка агрегатов без PII; versioned baseline; методика утверждена владельцем [behavioral: `tests/behavioral/test_rm_tech_281.py`]</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5883,14 +5895,14 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-001; SC: -; DEC: -. Evidence: new behavioral; methodology doc. Риск регрессии: средний. prerequisite RM-TECH-280 (OD-023 approved 2026-08-31) - planned по зависимости.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-286</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5905,16 +5917,16 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
+          <t>Attribution &amp; sales lift: test/control, versioned baseline, pilot lift report</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-246</t>
+          <t>RM-TECH-281, RM-TECH-229</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5929,7 +5941,7 @@
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
+          <t>pilot lift report по test/control с explainable методикой; RLS scope [behavioral: `tests/behavioral/test_rm_tech_282.py`]</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5939,14 +5951,14 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-002; SC: -; DEC: DEC-005, DEC-027. Evidence: new behavioral; report. Риск регрессии: средний. blocked OD-014 (DEC-027); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-287</t>
+          <t>RM-TECH-283</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5956,21 +5968,21 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
+          <t>Prerequisite: audience source/privacy contract (анонимные store-атрибуты, 152-ФЗ, OD-032)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>RM-STAB-013</t>
+          <t>RM-TECH-280, RM-TECH-253</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5982,10 +5994,14 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>scope_decision</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
+          <t>privacy/legal решение (OD-032) и контракт источника утверждены [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -5995,14 +6011,14 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-005; SC: -; DEC: DEC-005, DEC-019. Evidence: OD-032; contract. Риск регрессии: низкий. blocked OD-032 (DEC-019); OD-023 approved 2026-08-31.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-288</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6012,21 +6028,21 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>nfr-slo.yaml + load-profiles.yaml (AG): method, percentile, error budget, generator, CI evidence</t>
+          <t>A/B attribution и winner metric (minimum sample, owner approval результата)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-205</t>
+          <t>RM-TECH-282</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6035,13 +6051,13 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>каждый SLO имеет window/denominator/exclusions; load generator и прогон в CI/стенде [artifact: `nfr-slo.yaml`]</t>
+          <t>A/B фиксирует группы/период/метрику; winner только при minimum sample и ручном утверждении [behavioral: `tests/behavioral/test_rm_tech_284.py`]</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6051,14 +6067,14 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-012, REQ-V26-010; SC: -; DEC: DEC-027. Evidence: new behavioral. Риск регрессии: средний. blocked OD-014 (DEC-027) - методика winner metric не утверждена.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-289</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6068,21 +6084,21 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
+          <t>Competitive separation: competitive_category, интервал/исключение в playlist/manifest (исключение §3.1 по OD-018)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-220</t>
+          <t>RM-TECH-202, RM-TECH-280</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6097,7 +6113,7 @@
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
+          <t>separation block/override test; изменение priority engine ограничено §3.1 [behavioral: `tests/behavioral/test_rm_tech_285.py`]</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6107,14 +6123,14 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-004; SC: -; DEC: DEC-005, DEC-022. Evidence: new behavioral. Риск регрессии: высокий: priority engine. OD-023 approved 2026-08-31, DEC-022 = OD-018 approved - planned после RM-TECH-280.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RM-UX-010</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6129,16 +6145,16 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
+          <t>Financial-system exchange: versioned/idempotent export + payment-status contract (после DEC-017)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>RM-BIZ-003</t>
+          <t>RM-TECH-246</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6147,13 +6163,13 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
+          <t>idempotent export round-trip; повтор не создаёт дубликатов; scope финансового контура зафиксирован [behavioral: `tests/behavioral/test_rm_tech_286.py`]</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6163,34 +6179,34 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-006, REQ-BIZ-009; SC: -; DEC: DEC-017. Evidence: new behavioral. Риск регрессии: средний. blocked OD-030.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-TECH-287</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Production readiness</t>
+          <t>BI/export/SIEM/vendor API: scoped keys, rate-limit, immutable audit, circuit breaker (после DEC-013)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-003</t>
+          <t>RM-STAB-013</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
@@ -6203,17 +6219,13 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>не запускается автоматически после pilot [owner]</t>
+          <t>401/403/429 negative; vendor connector с отдельными credentials и failure mode [behavioral: `tests/test_s065_rate_limit.py`]</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6223,38 +6235,38 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-INT-003; SC: SC-SEC-002; DEC: DEC-013. Evidence: tests/test_s065_rate_limit.py; new behavioral. Риск регрессии: средний. blocked OD-026.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-002</t>
+          <t>RM-TECH-289</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
+          <t>Extension points designed-not-implemented: ADR для programmatic (V26-007) и external measurement (V26-011)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-TECH-220</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6269,7 +6281,7 @@
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
+          <t>ADR принят с пометкой designed-not-implemented; код не пишется до OD-021/OD-031 [artifact: `docs/audit/RM-TECH-289-artifact.md (создаётся задачей)`]</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6279,38 +6291,38 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-V26-007, REQ-V26-011; SC: SC-ARCH-006; DEC: DEC-001, DEC-018. Evidence: ADR. Риск регрессии: низкий.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-003</t>
+          <t>RM-UX-010</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>POPS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>external-plan</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
+          <t>Service-quality reporting: доля active devices/logical carriers, plan/fact по каналу (analytics.compare)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-001</t>
+          <t>RM-BIZ-003</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6319,17 +6331,13 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>отчёт по каналу с долями и причинами; RLS scope advertiser [ui_smoke: `tests/ui-smoke/test_rm_ux_010.py`]</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6339,14 +6347,14 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-BIZ-004; SC: -; DEC: -. Evidence: новый ui-smoke; tests/behavioral/test_pop_reporting_scope.py. Риск регрессии: средний.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6356,21 +6364,21 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>external</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+          <t>Production readiness</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-002</t>
+          <t>RM-PILOT-003</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -6379,13 +6387,17 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
+          <t>не запускается автоматически после pilot [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой; OD-025/OD-028)`]</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6395,14 +6407,14 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): зависит от OD-025 (RTO/RPO) и OD-028 (топология); REQ-OPS-005/006; HA baseline выделен в RM-OPS-003</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-005</t>
+          <t>RM-OPS-002</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6412,17 +6424,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>retention-policy.yaml + legal decision register (AG): сроки, 152-ФЗ, deletion/archive, review date</t>
+          <t>Network segmentation: firewall rules по environment + negative reachability tests из device-сегмента</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-253</t>
+          <t>RM-PILOT-002</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
@@ -6435,17 +6447,13 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>scope_decision</t>
-        </is>
-      </c>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>юридическое утверждение retention/152-ФЗ (OD-009) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
+          <t>Admin API/PostgreSQL/MinIO/Redis недостижимы из device-сегмента; Gateway только HTTPS/mTLS [command: `python3 scripts/ci/roadmap-governance-guard.py`]</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6455,14 +6463,14 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-008; SC: SC-SEC-006; DEC: -. Evidence: reachability test log. Риск регрессии: средний: сеть пилота.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RM-PILOT-001</t>
+          <t>RM-OPS-003</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6472,21 +6480,21 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>external-plan</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Managed control-plane pilot scope</t>
+          <t>Production HA baseline: ≥2 backend, масштабируемый Gateway, standby PostgreSQL, MinIO replication, quarterly restore drill</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Gate-S, Gate-U, RM-ENV-001</t>
+          <t>RM-OPS-001</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -6495,13 +6503,17 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+          <t>production config gate зелёный; restore drill выполнен и записан [command: `tests/test_production_config_gate.py`]; топология утверждена (OD-028), RTO/RPO (OD-025) [owner: `docs/product/roadmap.yaml:owner_decisions (ACCEPT владельца с датой)`]</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6511,38 +6523,38 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-006, REQ-ARCH-004; SC: SC-OPS-001, SC-OPS-005; DEC: DEC-012, DEC-015. Evidence: tests/test_production_config_gate.py; drill record. Риск регрессии: высокий. blocked OD-025/OD-028.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>RM-OPS-004</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Rollout entity/state machine и feature flags: planned→lab→canary→staged→paused→completed/rolled_back</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>POPS</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>external-plan</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Deployment plan/preflight</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>RM-PILOT-001</t>
-        </is>
-      </c>
       <c r="F107" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -6551,13 +6563,13 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+          <t>rollback возвращает предыдущую версию; flag отключает функцию; ответственность по OD-010 [behavioral: `tests/integration/test_stand_rollback_drill.py`]</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6567,65 +6579,177 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-OPS-002; SC: SC-OPS-007; DEC: DEC-008. Evidence: tests/integration/test_stand_rollback_drill.py. Риск регрессии: средний. blocked OD-010.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Managed control-plane pilot scope</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Gate-S, Gate-U, RM-ENV-001</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>exact bundle/host/rollback/TLS [artifact: `docs/runbook/pilot-scope.md`]</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): deps += OD-024 (exit criteria ступеней), REQ-ARCH-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-002</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>POPS</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>external-plan</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Deployment plan/preflight</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>RM-PILOT-001</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>immutable lock, backup/restore, migration rehearsal, secrets/TLS/monitoring [artifact: `infra/deploy/images.lock.json + dry-run evidence`]</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
           <t>RM-PILOT-003</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>POPS</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Controlled pilot deploy</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>RM-PILOT-002</t>
         </is>
       </c>
-      <c r="F108" s="2" t="n">
+      <c r="F110" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>deployment</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner]</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>SHA/lock/schema/health, stand-safe journeys, rollback readiness [owner: `docs/audit/&lt;дата&gt;-pilot-deploy-&lt;sha&gt;.md + ACCEPT владельца с датой (deployment gate)`]</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
         </is>
@@ -6642,7 +6766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7988,7 +8112,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>commerce.booking</t>
+          <t>campaign.underdelivery</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7998,7 +8122,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Бронирование (offered→booked)</t>
+          <t>Разбор недопоказа и make-good (причина, процент, докрутка, компенсация)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -8008,27 +8132,27 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__campaign__underdelivery</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8036,14 +8160,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-201 (OD-040, US-UDR-001, ТЗ v2.6 r427); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-201</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-201 (US-UDR-001) и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>commerce.offer_generate</t>
+          <t>carrier.manage</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -8053,7 +8189,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Генерация коммерческого предложения (draft→offered)</t>
+          <t>Единый Operations-контур: physical device, logical carrier и surface всех каналов (scope, состояние, действия с подтверждением)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -8063,27 +8199,27 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__carrier__manage</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8091,14 +8227,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-255 (OD-040, US-CHAN-003, ТЗ v2.6 r427); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-255, RM-TECH-207A</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-255 (US-CHAN-003) и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>commerce.order_close</t>
+          <t>channel.register</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8108,7 +8256,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Закрытие заказа (terminal)</t>
+          <t>Регистрация channel/device/surface/profile и adapter contract (mock-проверка канала)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -8118,27 +8266,27 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__channel__register</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8146,14 +8294,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-207A (OD-040, US-CHAN-001, ТЗ v2.6 r427); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207A, RM-TECH-244</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-207A (US-CHAN-001) и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>commerce.order_create</t>
+          <t>channel.rendition_validate</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -8163,7 +8323,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Создание коммерческого заказа</t>
+          <t>Renditions и channel-specific ограничения: валидация preview, публикация версии без изменения core campaign</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -8173,27 +8333,27 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs (tab: Заказы)</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__order_create</t>
+          <t>test_uismoke__channel__rendition_validate</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8201,14 +8361,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-204 (OD-040, US-CHAN-002, ТЗ v2.6 r427); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-204, RM-TECH-207A</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-204 (US-CHAN-002) и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>commerce.payment_status</t>
+          <t>commerce.booking</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8218,7 +8390,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Статус оплаты заказа</t>
+          <t>Бронирование (offered→booked)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -8263,7 +8435,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>commerce.price_list_manage</t>
+          <t>commerce.offer_generate</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -8273,7 +8445,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Управление версиями прайс-листов</t>
+          <t>Генерация коммерческого предложения (draft→offered)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -8283,12 +8455,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__tariff_manage</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8318,7 +8490,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>commerce.tariff_manage</t>
+          <t>commerce.order_close</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8328,7 +8500,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Управление тарифами и прайс-листами</t>
+          <t>Закрытие заказа (terminal)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8338,12 +8510,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>/commerce/tariffs</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__commerce__tariff_manage</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8373,7 +8545,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>creative.moderate_approve</t>
+          <t>commerce.order_create</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -8383,22 +8555,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Одобрить креатив (модерация)</t>
+          <t>Создание коммерческого заказа</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__creative__moderate_approve</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8428,7 +8600,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>creative.moderate_reject</t>
+          <t>commerce.payment_status</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8438,22 +8610,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Отклонить креатив с причиной (модерация)</t>
+          <t>Статус оплаты заказа</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/commerce/tariffs (tab: Заказы)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__creative__moderate_reject</t>
+          <t>test_uismoke__commerce__order_create</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8483,7 +8655,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>creative.upload</t>
+          <t>commerce.price_list_manage</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -8493,22 +8665,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Загрузка креатива</t>
+          <t>Управление версиями прайс-листов</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__creative__upload</t>
+          <t>test_uismoke__commerce__tariff_manage</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8538,7 +8710,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>device.health_view</t>
+          <t>commerce.tariff_manage</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8548,7 +8720,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Видеть состояние парка устройств</t>
+          <t>Управление тарифами и прайс-листами</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -8558,12 +8730,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>/commerce/tariffs</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__device__health_view</t>
+          <t>test_uismoke__commerce__tariff_manage</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8593,7 +8765,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>emergency.activate</t>
+          <t>creative.moderate_approve</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -8603,7 +8775,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Экстренно остановить показ</t>
+          <t>Одобрить креатив (модерация)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -8618,7 +8790,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__emergency__activate</t>
+          <t>test_uismoke__creative__moderate_approve</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8641,18 +8813,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Platform/backend emergency state + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
-        </is>
-      </c>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>emergency.deactivate</t>
+          <t>creative.moderate_reject</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8662,7 +8830,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Снять аварийный режим</t>
+          <t>Отклонить креатив с причиной (модерация)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -8677,7 +8845,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__emergency__deactivate</t>
+          <t>test_uismoke__creative__moderate_reject</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8700,18 +8868,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Platform/backend deactivation + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
-        </is>
-      </c>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>experiment.evaluate</t>
+          <t>creative.upload</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -8721,12 +8885,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>A/B: группы, период, winner metric, ручное утверждение результата</t>
+          <t>Загрузка креатива</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -8736,22 +8900,22 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__experiment__evaluate</t>
+          <t>test_uismoke__creative__upload</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8759,26 +8923,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Запланировано задачей RM-TECH-284 (ТЗ v2.6 r421); реализации и smoke нет.</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-284</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>функция реализована задачей RM-TECH-284 и имеет зелёный smoke/behavioral proof</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>field_ops.device_confirm</t>
+          <t>data.catalog</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -8788,12 +8940,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Полевые операции: устройства магазина, фото, инциденты (mobile web)</t>
+          <t>Каталог данных: owner, PII-класс, retention и lineage сущности; контроль доступа/архива/удаления</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -8803,7 +8955,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__field_ops__device_confirm</t>
+          <t>test_uismoke__data__catalog</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8828,24 +8980,24 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-TECH-263 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+          <t>Запланировано задачей RM-TECH-251 (OD-040, US-DATA-001, ТЗ v2.6 r427); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-263</t>
+          <t>RM-TECH-251</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-TECH-263 и имеет зелёный smoke/behavioral proof</t>
+          <t>функция реализована задачей RM-TECH-251 (US-DATA-001) и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>finance.reconcile</t>
+          <t>device.health_view</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -8855,12 +9007,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Финансовая сверка: заказ/договор/тариф/price list</t>
+          <t>Видеть состояние парка устройств</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8870,22 +9022,22 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__finance__reconcile</t>
+          <t>test_uismoke__device__health_view</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -8893,26 +9045,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Запланировано задачей RM-TECH-286 (ТЗ v2.6 r421); реализации и smoke нет.</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-286</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>функция реализована задачей RM-TECH-286 и имеет зелёный smoke/behavioral proof</t>
-        </is>
-      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>inventory.rule_create</t>
+          <t>emergency.activate</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -8922,12 +9062,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Создать правило инвентаря</t>
+          <t>Экстренно остановить показ</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -8937,7 +9077,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__inventory__rule_create</t>
+          <t>test_uismoke__emergency__activate</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -8960,14 +9100,18 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Platform/backend emergency state + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>inventory.simulate</t>
+          <t>emergency.deactivate</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -8977,12 +9121,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Прогноз показов (симуляция инвентаря)</t>
+          <t>Снять аварийный режим</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8992,7 +9136,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__inventory__simulate</t>
+          <t>test_uismoke__emergency__deactivate</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9015,14 +9159,18 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Platform/backend deactivation + audit/outbox. Player-side enforcement deferred (KSO runtime).</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>kpi.review</t>
+          <t>experiment.evaluate</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -9032,7 +9180,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Бизнес-KPI: baseline/target/metric по целям §1.2</t>
+          <t>A/B: группы, период, winner metric, ручное утверждение результата</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9047,7 +9195,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__kpi__review</t>
+          <t>test_uismoke__experiment__evaluate</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9072,24 +9220,24 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-TECH-256 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+          <t>Запланировано задачей RM-TECH-284 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-256</t>
+          <t>RM-TECH-284</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-TECH-256 и имеет зелёный smoke/behavioral proof</t>
+          <t>функция реализована задачей RM-TECH-284 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>placement.audience_targeting</t>
+          <t>field_ops.device_confirm</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -9099,7 +9247,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Store-audience targeting по анонимным атрибутам магазина</t>
+          <t>Полевые операции: устройства магазина, фото, инциденты (mobile web)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9114,7 +9262,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__placement__audience_targeting</t>
+          <t>test_uismoke__field_ops__device_confirm</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -9139,24 +9287,24 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-TECH-283 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+          <t>Запланировано задачей RM-TECH-263 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-283</t>
+          <t>RM-TECH-263</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-TECH-283 и имеет зелёный smoke/behavioral proof</t>
+          <t>функция реализована задачей RM-TECH-263 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>rollout.rollback</t>
+          <t>finance.reconcile</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -9166,12 +9314,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Staged rollout и rollback с feature flags</t>
+          <t>Финансовая сверка: заказ/договор/тариф/price list</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9181,7 +9329,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__rollout__rollback</t>
+          <t>test_uismoke__finance__reconcile</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -9206,24 +9354,24 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-OPS-004 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+          <t>Запланировано задачей RM-TECH-286 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RM-OPS-004</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-OPS-004 и имеет зелёный smoke/behavioral proof</t>
+          <t>функция реализована задачей RM-TECH-286 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>system.theme_switch</t>
+          <t>inventory.priority</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -9233,37 +9381,37 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Переключение темы (light/dark)</t>
+          <t>Тип кампании и приоритеты с объяснимым preemption (действующая версия правил)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sidebar footer toggle</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__system__theme_switch</t>
+          <t>test_uismoke__inventory__priority</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -9271,14 +9419,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-202 (OD-040, US-PRI-001, ТЗ v2.6 r427); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-202</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-202 (US-PRI-001) и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>user.assign_roles</t>
+          <t>inventory.rule_create</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -9288,12 +9448,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Назначить роли/права пользователю</t>
+          <t>Создать правило инвентаря</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9303,7 +9463,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__assign_roles</t>
+          <t>test_uismoke__inventory__rule_create</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9333,7 +9493,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>user.create_advertiser</t>
+          <t>inventory.simulate</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -9343,12 +9503,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Завести локального рекламодателя</t>
+          <t>Прогноз показов (симуляция инвентаря)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9358,7 +9518,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__create_advertiser</t>
+          <t>test_uismoke__inventory__simulate</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9388,7 +9548,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>user.deactivate</t>
+          <t>kpi.review</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -9398,12 +9558,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Заблокировать пользователя</t>
+          <t>Бизнес-KPI: baseline/target/metric по целям §1.2</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -9413,22 +9573,22 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__deactivate</t>
+          <t>test_uismoke__kpi__review</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -9436,14 +9596,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-256 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-256</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-256 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>user.reset_password</t>
+          <t>placement.audience_targeting</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -9453,12 +9625,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Сбросить пароль пользователю</t>
+          <t>Store-audience targeting по анонимным атрибутам магазина</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -9468,22 +9640,22 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__reset_password</t>
+          <t>test_uismoke__placement__audience_targeting</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -9491,14 +9663,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-283 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-283</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-283 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>user.split_internal_advertiser</t>
+          <t>rollout.rollback</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -9508,7 +9692,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Разделить пользователей на внутренних и рекламодателей</t>
+          <t>Staged rollout и rollback с feature flags</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -9523,22 +9707,22 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__user__split_internal_advertiser</t>
+          <t>test_uismoke__rollout__rollback</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -9546,39 +9730,51 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-OPS-004 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>RM-OPS-004</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-OPS-004 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>self.apply_or_brief</t>
+          <t>system.theme_switch</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Подать заявку/бриф (кабинет рекламодателя)</t>
+          <t>Переключение темы (light/dark)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>/login</t>
+          <t>sidebar footer toggle</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__apply_or_brief</t>
+          <t>test_uismoke__system__theme_switch</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -9608,22 +9804,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>self.campaign_create</t>
+          <t>user.assign_roles</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Самому завести кампанию (self-service, P2)</t>
+          <t>Назначить роли/права пользователю</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -9633,22 +9829,22 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__campaign_create</t>
+          <t>test_uismoke__user__assign_roles</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -9656,36 +9852,24 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>UI-smoke отсутствует. P2 — self-service фаза, не пилот.</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>RM-BIZ-002</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>владелец включает self-service в scope пилота</t>
-        </is>
-      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>self.campaign_view</t>
+          <t>user.create_advertiser</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Смотреть свои кампании (кабинет рекламодателя)</t>
+          <t>Завести локального рекламодателя</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -9700,7 +9884,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__campaign_view</t>
+          <t>test_uismoke__user__create_advertiser</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -9730,32 +9914,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>self.login</t>
+          <t>user.deactivate</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Войти в кабинет рекламодателя</t>
+          <t>Заблокировать пользователя</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>/login (advertiser-web) + /accept-invite/{token}</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__login</t>
+          <t>test_uismoke__user__deactivate</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -9785,17 +9969,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>self.report_view</t>
+          <t>user.reset_password</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>advertiser-web</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Смотреть отчёт план/факт (PoP) — кабинет рекламодателя</t>
+          <t>Сбросить пароль пользователю</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -9810,22 +9994,22 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__self__report_view</t>
+          <t>test_uismoke__user__reset_password</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -9833,36 +10017,24 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>UI-smoke отсутствует. Фронтенд advertiser-web не проходил аудит.</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>RM-BIZ-003</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>реальные PoP-события от плеера, а не симулятора</t>
-        </is>
-      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>advertiser.apply</t>
+          <t>user.split_internal_advertiser</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>admin-web</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Подать заявку на подключение (публичная форма)</t>
+          <t>Разделить пользователей на внутренних и рекламодателей</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -9872,12 +10044,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>/become-advertiser</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>test_uismoke__advertiser__apply</t>
+          <t>test_uismoke__user__split_internal_advertiser</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -9907,17 +10079,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>backup.restore</t>
+          <t>self.apply_or_brief</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Резервное копирование и восстановление</t>
+          <t>Подать заявку/бриф (кабинет рекламодателя)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -9927,22 +10099,22 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>001C-FU: test_restore_drill_verify.py (16 behavioral) + test_backup_restore_drill.py (27 negative matrix) — real PG+MinIO drill</t>
+          <t>test_uismoke__self__apply_or_brief</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -9955,28 +10127,24 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Pilot host restore drill всё ещё требуется перед реальным деплоем (001D/001E). NATS = excluded_replayable (outbox source of truth).</t>
-        </is>
-      </c>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>campaign.competitive_separation</t>
+          <t>self.campaign_create</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Competitive separation при построении playlist/manifest</t>
+          <t>Самому завести кампанию (self-service, P2)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -9986,12 +10154,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>behavioral: tests/behavioral/test_rm_tech_285.py</t>
+          <t>test_uismoke__self__campaign_create</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -10016,59 +10184,59 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-TECH-285 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+          <t>UI-smoke отсутствует. P2 — self-service фаза, не пилот.</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-285</t>
+          <t>RM-BIZ-002</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-TECH-285 и имеет зелёный smoke/behavioral proof</t>
+          <t>владелец включает self-service в scope пилота</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>campaign.complete</t>
+          <t>self.campaign_view</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Автоматическое завершение кампании по концу рейса</t>
+          <t>Смотреть свои кампании (кабинет рекламодателя)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>POST /campaigns/{id}/complete, POST /campaigns/complete-expired</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>n/a (service feature, no UI journey)</t>
+          <t>test_uismoke__self__campaign_view</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -10081,58 +10249,54 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>LIFECYCLE-COMPLETE-001-FU: real DB proof. 7 behavioral tests green. Orchestrator-worker maintenance tick (5 min). CampaignStatusHistory verified. Idempotency proven.</t>
-        </is>
-      </c>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>content.dynamic_binding</t>
+          <t>self.login</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Dynamic creative: подстановка master-confirmed price/promo</t>
+          <t>Войти в кабинет рекламодателя</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login (advertiser-web) + /accept-invite/{token}</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>behavioral: tests/behavioral/test_rm_tech_262.py</t>
+          <t>test_uismoke__self__login</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -10140,51 +10304,39 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Запланировано задачей RM-TECH-262 (ТЗ v2.6 r421); реализации и smoke нет.</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-262</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>функция реализована задачей RM-TECH-262 и имеет зелёный smoke/behavioral proof</t>
-        </is>
-      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>device.heartbeat</t>
+          <t>self.report_view</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>advertiser-web</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat устройств (health/статус)</t>
+          <t>Смотреть отчёт план/факт (PoP) — кабинет рекламодателя</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/login</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>EDGE-004 behavioral (12 тестов): test_edge004_*.py</t>
+          <t>test_uismoke__self__report_view</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -10199,7 +10351,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -10207,54 +10359,66 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>UI-smoke отсутствует. Фронтенд advertiser-web не проходил аудит.</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>RM-BIZ-003</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>реальные PoP-события от плеера, а не симулятора</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>device.onboard</t>
+          <t>advertiser.apply</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Онбординг устройства (device-code → JWT)</t>
+          <t>Подать заявку на подключение (публичная форма)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>/become-advertiser</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>EDGE-001 behavioral (13 тестов): test_edge001_*.py</t>
+          <t>test_uismoke__advertiser__apply</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -10262,26 +10426,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>OD-038 / RLS-CONTEXT-DEVICE-001: в production-path устройство получает 403 INVALID_CODE — маршрут без RLS-контекста; reachable держался под admin-маской тестов. Unblock: RM-TECH-210 (behavioral под runtime-ролью на PostgreSQL).</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-210</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под runtime-ролью на PostgreSQL без элевации (behavioral evidence)</t>
-        </is>
-      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>finance.exchange</t>
+          <t>backup.restore</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -10291,12 +10443,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Обмен с финансовой системой: idempotent export + payment-status</t>
+          <t>Резервное копирование и восстановление</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -10306,7 +10458,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>behavioral: tests/behavioral/test_rm_tech_286.py</t>
+          <t>001C-FU: test_restore_drill_verify.py (16 behavioral) + test_backup_restore_drill.py (27 negative matrix) — real PG+MinIO drill</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -10321,7 +10473,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -10331,24 +10483,16 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-TECH-286 (ТЗ v2.6 r421); реализации и smoke нет.</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-286</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>функция реализована задачей RM-TECH-286 и имеет зелёный smoke/behavioral proof</t>
-        </is>
-      </c>
+          <t>Pilot host restore drill всё ещё требуется перед реальным деплоем (001D/001E). NATS = excluded_replayable (outbox source of truth).</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>integration.reconcile</t>
+          <t>campaign.competitive_separation</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -10358,7 +10502,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Ingestion агрегатов чековых данных и сверка с master-данными</t>
+          <t>Competitive separation при построении playlist/manifest</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -10373,7 +10517,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>behavioral: tests/behavioral/test_rm_tech_281.py</t>
+          <t>behavioral: tests/behavioral/test_rm_tech_285.py</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -10398,24 +10542,24 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Запланировано задачей RM-TECH-281 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+          <t>Запланировано задачей RM-TECH-285 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-281</t>
+          <t>RM-TECH-285</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>функция реализована задачей RM-TECH-281 и имеет зелёный smoke/behavioral proof</t>
+          <t>функция реализована задачей RM-TECH-285 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>license.enforce</t>
+          <t>campaign.complete</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -10425,7 +10569,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Enforcement лицензии при device enrollment</t>
+          <t>Автоматическое завершение кампании по концу рейса</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -10435,12 +10579,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard (enrollment choke-point)</t>
+          <t>POST /campaigns/{id}/complete, POST /campaigns/complete-expired</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>test_license_enrollment.py (13 behavioral tests)</t>
+          <t>n/a (service feature, no UI journey)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -10463,14 +10607,18 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>LIFECYCLE-COMPLETE-001-FU: real DB proof. 7 behavioral tests green. Orchestrator-worker maintenance tick (5 min). CampaignStatusHistory verified. Idempotency proven.</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>license.report</t>
+          <t>content.dynamic_binding</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -10480,22 +10628,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Отчёт по лицензии (занятые/свободные seats + пик)</t>
+          <t>Dynamic creative: подстановка master-confirmed price/promo</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>GET /licenses/report?year&amp;month</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>test_license_report.py (16 behavioral tests)</t>
+          <t>behavioral: tests/behavioral/test_rm_tech_262.py</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -10510,7 +10658,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -10518,14 +10666,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-262 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-262</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-262 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>license.seat_release</t>
+          <t>device.heartbeat</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -10535,22 +10695,22 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Освобождение лицензионного seat при decommission</t>
+          <t>Heartbeat устройств (health/статус)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>POST /devices/{device_id}/decommission</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>test_license_decommission.py (13 behavioral tests)</t>
+          <t>EDGE-004 behavioral (12 тестов): test_edge004_*.py</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -10580,7 +10740,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>license.upload</t>
+          <t>device.onboard</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -10590,12 +10750,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Загрузка/установка лицензионного файла</t>
+          <t>Онбординг устройства (device-code → JWT)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -10605,7 +10765,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>EDGE-001 behavioral (13 тестов): test_edge001_*.py</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -10630,24 +10790,24 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Layer 2 (signed-license/JWS/CRL + UI upload) — не реализован.</t>
+          <t>OD-038 / RLS-CONTEXT-DEVICE-001: в production-path устройство получает 403 INVALID_CODE — маршрут без RLS-контекста; reachable держался под admin-маской тестов. Unblock: RM-TECH-210 (behavioral под runtime-ролью на PostgreSQL).</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-210</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>signed-license Layer 2: upload .lic + проверка подписи</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под runtime-ролью на PostgreSQL без элевации (behavioral evidence)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>license.view</t>
+          <t>finance.exchange</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -10657,12 +10817,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Просмотр активных лицензий (UI)</t>
+          <t>Обмен с финансовой системой: idempotent export + payment-status</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -10672,7 +10832,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>behavioral: tests/behavioral/test_rm_tech_286.py</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -10697,24 +10857,24 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Layer 2 (signed-license/UI) — не реализован.</t>
+          <t>Запланировано задачей RM-TECH-286 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>RM-TECH-208</t>
+          <t>RM-TECH-286</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>signed-license Layer 2: offline Ed25519 verify + kid/CRL</t>
+          <t>функция реализована задачей RM-TECH-286 и имеет зелёный smoke/behavioral proof</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>manifest.deliver</t>
+          <t>integration.reconcile</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -10724,12 +10884,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Доставка манифеста на устройство</t>
+          <t>Ingestion агрегатов чековых данных и сверка с master-данными</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -10739,7 +10899,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>EDGE-002 behavioral (13 тестов): test_edge002_*.py</t>
+          <t>behavioral: tests/behavioral/test_rm_tech_281.py</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -10754,7 +10914,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>reachable</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -10762,14 +10922,26 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Запланировано задачей RM-TECH-281 (ТЗ v2.6 r421); реализации и smoke нет.</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-281</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>функция реализована задачей RM-TECH-281 и имеет зелёный smoke/behavioral proof</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>observability</t>
+          <t>license.enforce</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -10779,7 +10951,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Мониторинг и метрики (Prometheus/Grafana)</t>
+          <t>Enforcement лицензии при device enrollment</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -10789,12 +10961,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /device/onboard (enrollment choke-point)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>S-047: /metrics endpoint, Prometheus alert rules (8 rules)</t>
+          <t>test_license_enrollment.py (13 behavioral tests)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -10817,18 +10989,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>AlertManager routing deferred, но метрики и алерты существуют.</t>
-        </is>
-      </c>
+      <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>playlist.build</t>
+          <t>license.report</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -10838,7 +11006,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Построение плейлиста из манифеста</t>
+          <t>Отчёт по лицензии (занятые/свободные seats + пик)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -10848,12 +11016,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>GET /licenses/report?year&amp;month</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>test_license_report.py (16 behavioral tests)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -10868,7 +11036,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -10876,26 +11044,14 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Плеер не перенесён в enterprise. Код есть в старом репо (PLAYER-AUD-001), адаптация — после manifest/onboard/ingest.</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-207B</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>плеер перенесён в enterprise-репозиторий и есть реальный КСО</t>
-        </is>
-      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>pop.ingest</t>
+          <t>license.seat_release</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -10905,22 +11061,22 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Приём PoP-событий от устройств</t>
+          <t>Освобождение лицензионного seat при decommission</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>POST /devices/{device_id}/decommission</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>EDGE-003 behavioral (11 тестов): test_edge003_*.py</t>
+          <t>test_license_decommission.py (13 behavioral tests)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -10950,65 +11106,435 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>license.upload</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Загрузка/установка лицензионного файла</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Layer 2 (signed-license/JWS/CRL + UI upload) — не реализован.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-208</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>signed-license Layer 2: upload .lic + проверка подписи</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>license.view</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Просмотр активных лицензий (UI)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Layer 2 (signed-license/UI) — не реализован.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-208</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>signed-license Layer 2: offline Ed25519 verify + kid/CRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>manifest.deliver</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Доставка манифеста на устройство</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>EDGE-002 behavioral (13 тестов): test_edge002_*.py</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>observability</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Мониторинг и метрики (Prometheus/Grafana)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>S-047: /metrics endpoint, Prometheus alert rules (8 rules)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>AlertManager routing deferred, но метрики и алерты существуют.</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>playlist.build</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Построение плейлиста из манифеста</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Плеер не перенесён в enterprise. Код есть в старом репо (PLAYER-AUD-001), адаптация — после manifest/onboard/ingest.</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>RM-TECH-207B</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>плеер перенесён в enterprise-репозиторий и есть реальный КСО</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>pop.ingest</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Приём PoP-событий от устройств</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>EDGE-003 behavioral (11 тестов): test_edge003_*.py</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>reachable</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>не заявлено</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
           <t>release.rollback</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Rollback релиза по плану развёртывания</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>behavioral: tests/behavioral/test_rm_ops_004.py</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>Запланировано задачей RM-OPS-004 (ТЗ v2.6 r421); реализации и smoke нет.</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>RM-OPS-004</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>функция реализована задачей RM-OPS-004 и имеет зелёный smoke/behavioral proof</t>
         </is>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33390628743</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33390628743</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-004; SC: SC-OPS-001; DEC: DEC-015. Evidence: guard env; inventory diff. Риск регрессии: низкий. Закрывает Gate-E0 (RM-GOV-012, 2026-08-31).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-004; SC: SC-OPS-001; DEC: DEC-015. Evidence: guard env; inventory diff. Риск регрессии: низкий. Закрывает Gate-E0 (RM-GOV-012, 2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): environment-inventory.yaml содержит AG-поля для stand-81 (endpoint/версии/git SHA/schema/доступность без секретов, health/live+ready, MinIO, device-gateway loopback); приёмка - внутри задачи после закрытия RM-ENV-002.</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): нормативный формат journeys registry - docs/product/journeys/journeys.yaml (as-built из registry/user-journeys/AP); computed count = 79. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-004; SC: SC-SEC-011; DEC: DEC-007. Evidence: OD-009; retention-policy.yaml. Риск регрессии: низкий. blocked OD-009. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено POPS → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). 2026-08-31: кандидат docs/product/retention-policy.yaml подготовлен (working defaults REQ-DATA-001, legal register) - не действует до OD-009; задача остаётся blocked.</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): REQ-NFR-001/006/007; пороги ждут OD-011/OD-009 — добавить в notes; артефакты AG выносятся в RM-TECH-288 RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/slo-objectives.yaml - 11 объектов, каждое число §8 с formula/window/owner/status; пороги OD-011/OD-025 open. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-ARCH-001, REQ-API-001; SC: SC-API-001, SC-ARCH-003; DEC: -. Evidence: generated openapi.json diff; contract tests. Риск регрессии: средний: выявит смешение {id}/{code}. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/api/openapi-as-built-v1.json (113 paths/128 ops/149 схем), target docs/architecture/api/openapi-target-v2.6.md, envelope docs/architecture/events/event-envelope-v1.schema.json; contract tests и версионирование - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id.</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-DATA-002, REQ-V26-001; SC: SC-DATA-003; DEC: -. Evidence: tests/behavioral/test_adr018_multitenancy_rls.py; generated ERD. Риск регрессии: средний: backfill retailer_id. Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/architecture/erd/data-dictionary-as-built.md (62 таблицы, 38 RLS) и кандидат docs/architecture/erd/migration-plan-v2.6.md (§13 → present/missing → задачи); PII/retention колонки - RM-TECH-253/RM-OPS-005. Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31).</t>
+          <t>RM-GOV-012 (предложение 2026-08-31): AG требует channel-capability-matrix до старта разработки, а RM-TECH-261 держит матрицу за решением OD-021 (второй канал). Первый канал KSO описывается без OD-021; RM-TECH-261 расширяет матрицу вторым каналом. REQ: REQ-CHAN-001, REQ-CHAN-002, REQ-CHAN-003; SC: SC-CHAN-002; DEC: DEC-001 (расширение). Evidence: артефакт; ACCEPT владельца. Риск регрессии: нет (документ). Утверждена OD-042 (2026-08-31). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): docs/product/channel-capability-matrix.yaml (KSO + declared каналы §7); приёмка - внутри задачи после Gate-S.</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-NFR-001, REQ-NFR-006, REQ-NFR-007, REQ-NFR-005; SC: SC-NFR-001, SC-NFR-005, SC-NFR-006, SC-NFR-007; DEC: DEC-006, DEC-009. Evidence: load run report; nfr-slo.yaml. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено A → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки):ы docs/product/nfr-slo.yaml и docs/product/load-profiles.yaml (7 профилей); load generator отсутствует (new). Задача planned до закрытия зависимостей (OD-043).</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-UX-001, REQ-SEC-002; SC: SC-SEC-009; DEC: DEC-023. Evidence: generated matrices; guard registry. Риск регрессии: низкий. RM-GOV-012 (предложение 2026-08-31, до ACCEPT владельца): перенесено U → C - артефакт Дополнения AG принимается до Gate-C (старт разработки по OD-041). Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): as-built docs/product/role-scope-matrix.yaml (5 seeded ролей × 30 permissions, Q2 target 7 ролей, 38 RLS-таблиц, deny-cases), docs/product/portal-route-matrix.yaml (admin 16 + advertiser 9 маршрутов), docs/product/journeys/journeys.yaml (79 journeys, нормативный формат); generated-сверка guard - после старта задачи; задача planned до Gate-S (OD-043).</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · artifact · docs/architecture/rm-stab-003-personas-retailer-scope-design-gate.md</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений 2026-08-31 (стадия S, OD-043: RM-STAB-002 done): mini-design docs/architecture/rm-stab-003-personas-retailer-scope-design-gate.md - persona → bundle (30 существующих кодов) → retailer scope, миграция для RM-STAB-004, acceptance; 3 решения владельца D1-D3 (owner gate scope_decision). OD-044 (2026-08-31): D1-D3 приняты владельцем, gate scope_decision granted; verification до commit/CI.</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2)</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) OD-044 (2026-08-31): реализовать по mini-design RM-STAB-003 - 4 bundles аддитивно, alias operator, scope_type=retailer в resolve_scope_context/require_scoped_permission; D3 - retailer scope по умолчанию внутренним non-admin (seed); D2 - analyst read-only retailer-scoped; security_admin не трогать (D1 → RM-STAB-015).</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): нормативный формат journeys registry - docs/product/journeys/journeys.yaml (as-built из registry/user-journeys/AP); computed count = 79. Задача planned до закрытия зависимостей (OD-043).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): нормативный формат journeys registry - docs/product/journeys/journeys.yaml (as-built из registry/user-journeys/AP); computed count = 79. Задача planned до закрытия зависимостей (OD-043). 2026-08-31 старт (OD-043: RM-STAB-003 verification): journeys.yaml нормализован (Happy-path N, selectors из smoke, permission_codes), валидатор scripts/ci/check-journey-spec.py --strict (+self-test).</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004).</t>
+          <t>RM-GOV-009 кандидат A3 (OD-037). REQ: REQ-SEC-009; SC: SC-SEC-007; DEC: -. Evidence: tests/test_phase3_user_management.py; tests/test_s019_role_safety.py. Риск регрессии: средний: миграция permission-кодов затрагивает seed ролей (RM-STAB-004). OD-044 D1 (2026-08-31): сузить security_admin до модели Q2 (снять campaigns.manage/approve, creatives.moderate, inventory.manage, users.manage) отдельной миграцией с negative-тестами.</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md; ждёт CI-evidence и owner gate device_contract.</t>
         </is>
       </c>
     </row>

--- a/docs/product/generated/roadmap.generated.xlsx
+++ b/docs/product/generated/roadmap.generated.xlsx
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>verified · artifact · docs/architecture/rm-stab-003-personas-retailer-scope-design-gate.md</t>
+          <t>verified · artifact · docs/architecture/rm-stab-003-personas-retailer-scope-design-gate.md; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений 2026-08-31 (стадия S, OD-043: RM-STAB-002 done): mini-design docs/architecture/rm-stab-003-personas-retailer-scope-design-gate.md - persona → bundle (30 существующих кодов) → retailer scope, миграция для RM-STAB-004, acceptance; 3 решения владельца D1-D3 (owner gate scope_decision). OD-044 (2026-08-31): D1-D3 приняты владельцем, gate scope_decision granted; verification до commit/CI.</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) RM-GOV-009 (r421): добавить ссылки OD-035/DEC-023 (Q2: 7 ролей) и REQ-UX-001; acceptance без изменений 2026-08-31 (стадия S, OD-043: RM-STAB-002 done): mini-design docs/architecture/rm-stab-003-personas-retailer-scope-design-gate.md - persona → bundle (30 существующих кодов) → retailer scope, миграция для RM-STAB-004, acceptance; 3 решения владельца D1-D3 (owner gate scope_decision). OD-044 (2026-08-31): D1-D3 приняты владельцем, gate scope_decision granted; verification до commit/CI. done 2026-08-31: CI 33408891221 success (Git = истина).</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) OD-044 (2026-08-31): реализовать по mini-design RM-STAB-003 - 4 bundles аддитивно, alias operator, scope_type=retailer в resolve_scope_context/require_scoped_permission; D3 - retailer scope по умолчанию внутренним non-admin (seed); D2 - analyst read-only retailer-scoped; security_admin не трогать (D1 → RM-STAB-015).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) OD-044 (2026-08-31): реализовать по mini-design RM-STAB-003 - 4 bundles аддитивно, alias operator, scope_type=retailer в resolve_scope_context/require_scoped_permission; D3 - retailer scope по умолчанию внутренним non-admin (seed); D2 - analyst read-only retailer-scoped; security_admin не трогать (D1 → RM-STAB-015). 2026-08-31 старт (OD-043: RM-STAB-003/006 done; план владельца после CI 33408891221).</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · command · python3 scripts/ci/check-journey-spec.py --strict; verified · command · python3 scripts/roadmap-consistency-check.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): нормативный формат journeys registry - docs/product/journeys/journeys.yaml (as-built из registry/user-journeys/AP); computed count = 79. Задача planned до закрытия зависимостей (OD-043). 2026-08-31 старт (OD-043: RM-STAB-003 verification): journeys.yaml нормализован (Happy-path N, selectors из smoke, permission_codes), валидатор scripts/ci/check-journey-spec.py --strict (+self-test).</t>
+          <t>полная приёмка — docs/audit/2026-08-26-roadmap-task-breakdown-final-candidate.md (+v2) Кандидат подготовлен (OD-043, 2026-08-31, без приёмки): нормативный формат journeys registry - docs/product/journeys/journeys.yaml (as-built из registry/user-journeys/AP); computed count = 79. Задача planned до закрытия зависимостей (OD-043). 2026-08-31 старт (OD-043: RM-STAB-003 verification): journeys.yaml нормализован (Happy-path N, selectors из smoke, permission_codes), валидатор scripts/ci/check-journey-spec.py --strict (+self-test). done 2026-08-31: CI 33408891221 success; включение валидатора в CI-политику — RM-STAB-008.</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>done</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2401,17 +2401,17 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; прямой запрос к БД под ролью приложения без контекста находит активный код онбординга [behavioral: `tests/behavioral/test_rls_context_strictness.py`]</t>
+          <t>POST /device/onboard и POST /identity/device-codes работают под ролью приложения БЕЗ элевации до admin; обе записи снимаются из ENDPOINT_ELEVATION_ALLOWLIST, и behavioral-набор остаётся зелёным без них [behavioral: `tests/behavioral/test_edge001_device_onboarding.py`]; bootstrap-RLS миграции 037: без RLS-контекста роль приложения видит 0 onboarding codes (fail-closed); со своим app.rmp_device_code — только свою строку; с чужим кодом — 0 [behavioral: `tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap`]</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py; verified · behavioral · tests/behavioral/test_edge001_device_onboarding.py::TestRMTech210BootstrapRLS::test_app_role_sees_code_only_with_code_bootstrap; verified · behavioral · tests/behavioral/test_rls_context_strictness.py; verified · ci_run · https://github.com/santanas-dev/retail-media-platform-enterprise/actions/runs/33408891221</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md; ждёт CI-evidence и owner gate device_contract.</t>
+          <t>заведена по решению владельца 2026-08-26 после того, как RM-STAB-002 вскрыл дефект. RLS-CONTEXT-DEVICE-CODES-001 и RLS-CONTEXT-DEVICE-ONBOARD-001 — ни один из двух маршрутов не несёт Depends(set_rls_context), при этом оба работают с RLS-таблицей device_onboarding_codes. Доказано прямым запросом: владелец с admin видит код 1, роль приложения без контекста — 0, она же с admin — 1. Значит в проде каждое устройство получает 403 INVALID_CODE и self-onboarding не работает вовсе. Латентно только потому, что пилот не развёрнут. Блокирует device pilot: RM-TECH-207B и ветку RM-PILOT. Требует решения владельца по модели: онбординг неаутентифицирован, поэтому scope нельзя вывести из пользователя — нужен либо явный контекст под код, либо отдельная политика. 2026-08-31 (стадия S, OD-043: зависимость RM-STAB-002 done): реализовано локально - set_rls_context на /identity/device-codes, bootstrap-контекст кода/fingerprint на /device/onboard, миграция 037 (rehearsal down/up), allowlist элевации снят; targeted 97 passed под ролью приложения; design-gate docs/architecture/rm-tech-210-device-onboarding-rls-bootstrap-design-gate.md (на тот момент - до CI-evidence и owner gate). verification 2026-08-31: CI 33408891221 success (условием done тогда оставался owner gate device_contract). 2026-08-31: приёмка №2 уточнена владельцем — три утверждения bootstrap-RLS (без контекста 0; свой app.rmp_device_code — только свой; чужой — 0); ref → TestRMTech210BootstrapRLS. done 2026-08-31: owner gate device_contract granted - OD-045 (fail-closed контракт принят владельцем).</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>EDGE-001 behavioral (13 тестов): test_edge001_*.py</t>
+          <t>EDGE-001 behavioral (16 тестов, в т.ч. TestRMTech210BootstrapRLS): test_edge001_*.py</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>reachable</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -10788,21 +10788,9 @@
           <t>не заявлено</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>OD-038 / RLS-CONTEXT-DEVICE-001: в production-path устройство получает 403 INVALID_CODE — маршрут без RLS-контекста; reachable держался под admin-маской тестов. Unblock: RM-TECH-210 (behavioral под runtime-ролью на PostgreSQL).</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>RM-TECH-210</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>POST /device/onboard и POST /identity/device-codes работают под runtime-ролью на PostgreSQL без элевации (behavioral evidence)</t>
-        </is>
-      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
